--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44929</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45349</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45656</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>45228</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45674</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>44950</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>44518</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45212</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>44993</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>45575</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45111</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45681</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45824</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44973</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>44714</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44463</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45680</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>46174</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>46259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>46126</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>46126</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>46126</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>46281</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44853</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44595</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44508</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44461</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44593</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>45244</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>45575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44859</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45546</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44942</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44476</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45313</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45629</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45104</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44676</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44508</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44859</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>46030</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>45447</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45503</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>46085</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>46245</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44467</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>45708</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>44473</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44874</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44959</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45481</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46275</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45343</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45257</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44638</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45627</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44495</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44530</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44518</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44461</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44721</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44606</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>44889</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44607</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44480</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44509</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44733</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44461</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44783</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44458</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44825</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44844</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>44466</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>44607</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44818</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44647</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44487</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44510</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44753</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44866</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44729</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44528</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44522</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44783</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44781</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>44510</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44461</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44767</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>44764</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44480</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44480</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44610</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44756</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44509</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44776</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44463</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44467</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>44503</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>44530</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>44512</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>44637</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44733</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44501</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>44850</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44629</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44637</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44517</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>44831</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>44638</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44714</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44509</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>44474</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44637</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>44637</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44486</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>44461</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44796</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44514</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>44641</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>44523</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44592</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44650</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44497</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44859</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44945</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44687</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45348</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45373</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>44608</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>44608</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44608</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45224</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45162</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45078</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44859</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45517</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45343</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45307</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45035</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45715</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44497</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45741</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44631</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45656</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45453</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45453</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>44864</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>44950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>45254</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44474</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>44734</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>45115</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45115</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45208</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45453</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45510</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44487</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>44866</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45572</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45072</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44967</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45104</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44928</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44568</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45158</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45170</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45027</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44809</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45000</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>44593</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45708</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45198</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>45208</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45484</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45089</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45502</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45471</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44828</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>44865</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45817</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>45238</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46030</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44959</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45975</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45964</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>44503</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45211</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45439</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>45834</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45103</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>44610</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45817</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>44606</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45897</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45937</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44511</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45903</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45607</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45933</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45599</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45904</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45434</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45707</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45922</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44573</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45253</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45364</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44804</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45162</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45322</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45930</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>46142</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>46142</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>46142</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>46142</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45469</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45254</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45107</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45608</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44970</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45599</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>44655</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>45587</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45391</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45303</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>45105</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44573</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44734</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45327</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45958</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45525</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45964</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45790</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45964</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45964</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>44697</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45441</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>45246</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>44662</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45896</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45974</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45427</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45303</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44808</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>46154</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45198</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46157</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45986</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>44995</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45987</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45455</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45373</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45404</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44676</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>46163</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44909</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44753</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>46163</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>46153</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46163</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45994</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>46163</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>44999</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>44999</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45022</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46001</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45609</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45533</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45408</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44957</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45456</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44494</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>46010</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>46010</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>46007</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>44999</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>45301</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>44578</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>46058</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>46170</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45115</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>46170</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>46030</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>46030</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>44889</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>46030</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45226</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45664</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45664</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>46174</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45162</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>46174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>46030</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>46043</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>46042</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>46042</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>46042</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>46174</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44748</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>46174</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>46174</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44915</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>46045</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46171</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45510</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45473</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>44739</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45042</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45525</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45285</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>45481</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46069</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>46181</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45217</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46069</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46181</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>46071</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>46181</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44606</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>46182</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45385</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>46176</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>45132</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>46184</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44595</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46080</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45104</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>46184</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45104</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>46184</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>46185</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>46181</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>44487</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45572</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46185</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46185</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>44907</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46189</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>46189</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>46189</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45495</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45469</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>46095</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45511</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>46196</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>46196</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45190</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>46196</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>46198</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46198</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46198</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45235</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>45391</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>44615</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>44602</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>46112</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46184</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45719</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46112</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44791</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>46112</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>46120</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45448</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45506</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45191</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>44641</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>44999</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>45827</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>44463</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>45714</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45030</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>44812</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44609</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45072</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>44950</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>44950</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45586</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45267</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>44488</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>44552</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>46252</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45511</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46252</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46210</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>46252</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>46210</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46210</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>46210</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>45327</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>44844</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44995</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>46254</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46253</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45184</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>46216</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46216</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>44487</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44733</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45481</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>44501</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>46258</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44461</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>44642</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45254</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>44497</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>44641</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>46268</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45664</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>46268</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45777</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45601</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>45559</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45303</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>46230</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45470</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>46230</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>46230</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>46230</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46275</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>46275</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45407</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>46281</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>45667</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38923,7 +38923,7 @@
         <v>46237</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45617</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>45569</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>46230</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>46237</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>46230</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>46283</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45303</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39507,7 +39507,7 @@
         <v>45720</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>45680</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45825</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>45485</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>45485</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45485</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44498</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>44662</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>44648</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>44739</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>45733</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>45642</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>44855</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45835</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45257</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45572</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45742</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>43993</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>44655</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>46219</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>46267</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>46268</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>46126</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44929</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45349</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>44587</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45674</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45228</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45656</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45575</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>44993</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45824</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45111</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44812</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45810</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45212</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>46290</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45681</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44714</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>45680</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46185</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>44722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>46259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>46126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>46126</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>46126</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>46281</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44467</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45343</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>46030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44959</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>44676</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>46085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45447</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44476</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44645</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45257</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>45546</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45313</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45525</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>44593</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45575</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45708</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44473</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>46245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45674</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45244</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45104</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44508</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44942</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45627</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44495</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44530</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44721</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44491</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44606</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>44889</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>44607</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44480</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>44509</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>44783</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44733</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>44825</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>44844</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44466</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44607</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44818</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44647</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44510</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44487</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44753</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44866</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44729</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>44528</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44522</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44781</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44510</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44764</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>44767</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44480</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44480</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44610</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>44756</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44509</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44467</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>44776</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44503</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>44530</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>44733</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>44512</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44501</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44850</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>44629</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44637</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44517</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>44831</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>44638</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>44714</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44509</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44474</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44637</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44637</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44486</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44514</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44641</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44796</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>44523</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44650</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>44592</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44497</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>45042</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>45170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45572</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>44791</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45211</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45208</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45238</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44739</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>44864</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45254</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45373</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45391</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45453</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>44809</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>45469</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45455</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44497</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45481</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44957</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45533</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45484</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>44950</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>44950</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45720</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46030</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45680</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45303</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>46030</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>46030</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45235</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45427</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45586</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45481</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45817</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45817</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44999</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44999</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>46042</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>46042</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>46042</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45897</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44915</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>46043</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44642</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45903</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44552</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>44995</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45599</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45348</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45917</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45922</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>46069</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>46069</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44615</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45132</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45103</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46071</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44568</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>46080</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45930</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44676</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45408</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45587</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45385</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44593</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45404</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46095</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45105</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>44641</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>46112</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45958</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>46112</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46112</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45115</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45027</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45226</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45267</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>46120</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45964</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45964</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45964</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>44609</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46127</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>44828</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>44487</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45506</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45022</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44474</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44999</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45986</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45827</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45987</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45607</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45158</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>45994</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45904</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45656</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>44959</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45072</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44753</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45937</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44812</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45364</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>46001</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45975</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45322</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44748</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45834</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45719</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>46030</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>46010</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45825</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45517</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45933</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44498</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45642</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>44648</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45030</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45485</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45485</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44662</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44855</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44739</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45714</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45707</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45733</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>46142</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45485</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45511</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>44573</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45072</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45741</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>46142</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>44488</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>46142</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>46142</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44595</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45105</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45510</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44734</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46154</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45896</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>44859</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45790</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45303</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>45835</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>46157</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45391</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>46153</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45115</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45115</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>44608</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44503</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>46163</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46163</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>46163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46163</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44907</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45742</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45572</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>46058</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46007</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45257</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45254</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45609</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>46170</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>44487</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45525</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>46171</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45104</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46170</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>46174</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44558</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45078</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>46174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>46174</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>46174</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>46174</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45000</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45608</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>46181</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>44494</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45303</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>46181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>46181</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>46176</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45511</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>46184</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>46184</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>46184</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>46182</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>46185</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>46185</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>46185</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45572</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46181</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>44866</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46189</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>46189</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46189</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45190</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44608</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>44608</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44967</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>45327</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>46198</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45162</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>46196</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>46196</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>46196</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44578</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>46184</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>46198</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>46198</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45104</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44602</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44662</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45198</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44697</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>44606</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>44641</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>46252</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45217</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46210</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>46210</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45072</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>45191</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46210</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>46210</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45162</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>46253</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>45198</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>46254</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>46258</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45456</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44808</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46216</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>46216</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45254</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45208</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>44804</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45188</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45307</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45285</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>44734</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45448</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>46268</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>46268</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44687</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>45471</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>46230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>46230</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>46230</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>46230</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>46275</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>46275</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45007</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>46237</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>46237</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45301</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45441</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>44889</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>46281</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>46230</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45327</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44865</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>46230</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>45453</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45453</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>46283</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>45525</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44573</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>46287</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36438,7 +36438,7 @@
         <v>44610</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>44909</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>44928</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>44497</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36730,7 +36730,7 @@
         <v>45469</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>44859</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>44733</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45246</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>46289</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>46290</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>46290</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>46290</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45184</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>46290</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>46290</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>46290</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>46289</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>44511</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>44487</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44970</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45599</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>44606</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>44945</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44995</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45035</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>44655</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45373</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44844</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45502</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>45439</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45162</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45495</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44631</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45224</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45089</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>44501</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45664</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45664</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45434</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45715</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45664</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45708</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>45473</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45253</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>44999</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>45777</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45303</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45559</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45601</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45470</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45667</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45407</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45569</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45617</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>43993</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>44655</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>46219</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>46268</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>46267</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>46286</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>46288</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>46126</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44929</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>45092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45349</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>44587</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45674</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45228</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45656</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45575</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>44993</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45824</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45525</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45111</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44812</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45810</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45212</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>46290</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45681</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44714</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>45680</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46185</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>44722</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>46259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>46126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>46126</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>46126</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>46281</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44467</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45343</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>46030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44959</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>44676</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>46085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45447</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>44476</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44645</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>45257</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>45546</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45313</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45525</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>44593</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45575</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44859</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45708</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>46275</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44473</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45030</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>46245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45674</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45244</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45104</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44508</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44942</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>44638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45627</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44495</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44530</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44721</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44491</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44606</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>44889</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>44607</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44480</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>44509</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>44783</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>44733</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>44825</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44516</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>44844</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44466</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44607</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44818</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44647</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44510</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44487</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44753</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>44866</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44729</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>44528</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44522</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44781</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44510</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44764</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>44767</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44480</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44480</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44610</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>44756</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44509</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44467</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>44776</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44503</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>44530</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>44733</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>44512</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>44501</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44850</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>44629</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44637</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44517</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>44831</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>44638</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>44714</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>44509</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44474</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44637</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44637</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44486</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44514</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44641</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44796</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>44523</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44650</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>44592</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>44497</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>45042</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>45170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45572</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>44791</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45211</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45208</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45238</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>44739</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>44864</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45254</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45373</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45391</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45453</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>44809</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>45469</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45455</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44497</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45481</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44957</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45533</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45484</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>44950</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>44950</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45720</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46030</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45680</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45303</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>46030</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>46030</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45235</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45427</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45586</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45481</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45817</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45817</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44999</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>44999</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>46042</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>46042</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>46042</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45897</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44915</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>46043</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44642</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45903</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>44552</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>44995</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45599</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45348</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45917</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45922</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>46069</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>46069</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44615</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45132</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45103</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46071</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44568</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>46080</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45930</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44676</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45408</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45587</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45385</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44593</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45404</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46095</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45105</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>44641</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>46112</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45958</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>46112</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46112</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45115</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45027</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45226</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45267</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>46120</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45964</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45964</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45964</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>44609</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46127</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>44828</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>44487</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45506</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45022</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44474</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>44999</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45986</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45827</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45987</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45607</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45158</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>45994</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45904</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45656</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>44959</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45072</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44753</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45937</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44812</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45364</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>46001</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45975</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45322</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44748</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45834</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45719</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>46030</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>46010</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45825</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45517</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45933</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44498</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45642</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>44648</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45030</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45485</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45485</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>44662</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44855</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44739</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45714</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45707</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45733</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>46142</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45485</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45511</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>44573</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45072</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45741</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>46142</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>44488</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>46142</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>46142</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44595</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45105</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45510</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44734</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46154</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45896</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>44859</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45790</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45303</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>45835</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>46157</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45391</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>46153</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45115</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45115</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>44608</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44503</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>46163</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46163</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>46163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46163</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44907</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45742</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45572</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>46058</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46007</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45257</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45254</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
         <v>45609</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>46170</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>44487</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45525</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>46171</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45104</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>46170</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>46174</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28731,7 +28731,7 @@
         <v>44558</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45078</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>46174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>46174</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>46174</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>46174</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45000</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45608</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>46181</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>44494</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45303</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>46181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>46181</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>46176</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>45511</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>46184</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>46184</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>46184</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>46182</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>46185</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>46185</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>46185</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45572</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46181</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>44866</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46189</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>46189</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46189</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45190</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44608</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>44608</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44967</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>45327</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>46198</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45162</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>46196</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>46196</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>46196</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>44578</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>46184</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>46198</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>46198</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45104</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44602</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44662</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45198</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>44697</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>44606</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>44641</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>46252</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45217</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46210</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>46210</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45072</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>45191</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46210</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>46210</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45162</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>46253</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>45198</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>46254</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>46258</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>45456</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44808</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46216</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>46216</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45254</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45208</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>44804</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45188</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45307</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45285</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>44734</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45448</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>46268</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>46268</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44687</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>45471</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>46230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>46230</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>46230</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>46230</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>46275</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>46275</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45007</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>46237</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>46237</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45301</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45441</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>44889</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>46281</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>46230</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45327</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44865</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>46230</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>45453</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45453</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>46283</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>45525</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44573</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>46287</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36438,7 +36438,7 @@
         <v>44610</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>44909</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>44928</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>44497</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36730,7 +36730,7 @@
         <v>45469</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>44859</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>44733</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45246</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>46289</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>46290</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>46290</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>46290</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45184</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>46290</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>46290</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>46290</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>46289</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>44511</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>44487</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44970</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45599</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>44606</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>44945</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44995</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45035</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>44655</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45373</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44844</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45502</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>45439</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45162</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45495</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44631</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45224</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45089</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>44501</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45664</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45664</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45434</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45715</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45664</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45708</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>45473</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45253</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>44999</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>45777</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45303</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45559</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45601</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45470</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45667</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45407</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45569</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45617</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>43993</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>44655</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>46219</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>46268</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>46267</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>46286</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>46288</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>46126</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>46280</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45349</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45674</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>45656</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>44950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45228</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45212</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45681</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>44993</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>44812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45575</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45111</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>46290</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44714</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>45680</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46185</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46259</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>46126</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>46126</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>46126</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45258</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45343</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44593</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45244</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>45575</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>46085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>44859</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45546</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44942</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45257</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44645</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44476</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45313</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45629</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>45575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44676</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44508</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>44859</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45447</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45503</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>46245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>46030</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45708</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44473</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>44874</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44959</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45481</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44638</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45627</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44530</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44518</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44495</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44889</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44607</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44480</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44509</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44783</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44733</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44516</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44844</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44607</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>44818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44647</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44487</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44510</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44753</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44866</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44729</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44522</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44528</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44781</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44510</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44764</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44767</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44480</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44480</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44756</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44610</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44776</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44503</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44530</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44512</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44637</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44850</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44629</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44637</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44714</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44509</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44474</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>44637</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>44637</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>44486</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44796</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44514</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44641</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>44523</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44592</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44650</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44497</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44859</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44945</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45348</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44687</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45224</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45373</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45078</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44608</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44608</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44608</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45162</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44859</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45517</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45307</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45667</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45343</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45741</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44497</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45817</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45617</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45035</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44631</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45569</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45656</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46010</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45453</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45453</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>46010</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44864</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>44950</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44474</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45817</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45254</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45897</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>46030</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>46030</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>46030</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>45208</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>44734</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45115</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45115</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45903</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46030</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46043</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>46042</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>46042</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45303</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46042</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45599</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45720</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45453</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45680</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45917</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45510</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45922</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>44487</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44866</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45572</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45072</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45930</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44967</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45936</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44928</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>46069</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46069</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45104</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44568</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45158</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>46071</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45170</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45027</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>44809</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>46080</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45000</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44593</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44558</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45964</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>45708</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45964</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45964</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46095</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45198</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45208</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45974</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45484</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45089</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44828</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>44865</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>46112</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45502</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45471</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>46112</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>46112</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45986</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45825</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45987</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>46120</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45238</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45485</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45485</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45485</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44498</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>44662</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44648</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>44739</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45994</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45733</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45642</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44855</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45072</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>46127</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44503</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45211</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45105</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45835</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45439</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>45827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45103</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45714</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44610</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45030</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>44606</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44812</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45072</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44511</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>46030</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44959</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45975</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45964</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45257</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45742</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45434</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45834</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44573</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>45253</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44804</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45162</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45937</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45469</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45933</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45254</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45107</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45608</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44970</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45904</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45599</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>44655</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45707</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45587</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45391</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45364</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45303</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45322</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46142</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>46142</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>46142</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>46142</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44573</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45327</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44734</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45525</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45790</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44697</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45896</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>45964</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45441</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45303</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>46154</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>46157</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45246</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44662</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>46163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>46153</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46163</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>46163</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45427</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44808</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>46007</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>46058</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44995</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>46170</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46170</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>46174</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>46174</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>46174</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>46174</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>46174</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45455</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>46171</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45373</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45404</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44676</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44909</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>44753</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>46181</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>46181</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>46181</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>46182</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>46176</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>46184</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44999</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>44999</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46184</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>46184</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>46185</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45022</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46181</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>45609</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45533</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45408</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46185</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46189</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>46189</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>46189</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44957</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>46196</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45456</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>44494</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>46196</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>46196</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>46198</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32014,7 +32014,7 @@
         <v>44999</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>46198</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>46198</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45301</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44578</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46184</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45115</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44889</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45226</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45664</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45664</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45162</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>46210</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>46210</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>46210</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>46210</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44748</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>44915</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>46216</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>46216</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>46258</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>45510</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>45473</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44739</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45042</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45525</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45285</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45481</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45217</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>46268</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44606</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>46268</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>45385</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>45132</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>46230</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>46230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>46230</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>44595</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>46230</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45104</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45104</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>46275</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>46275</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>46281</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>46237</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44487</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>46230</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>46237</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45572</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>46230</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>44907</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>46283</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>45495</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45469</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45511</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46287</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45190</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45235</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45391</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44615</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>44602</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45719</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>44791</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>46289</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>46289</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>46290</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45448</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46290</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45506</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>46290</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45191</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>46290</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>44517</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>44641</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>46290</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46290</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>44999</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>46252</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>46252</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>46252</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44609</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>46297</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>46297</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>44950</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>44950</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46297</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45586</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>45267</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>46297</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>46297</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>44488</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46297</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>46297</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>46254</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44552</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>46297</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46297</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46297</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45511</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45327</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>44844</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>44995</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45184</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44487</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>44733</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45481</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44501</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44642</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45007</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>45254</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>44497</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>44641</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45664</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45777</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45601</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>45559</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>45303</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45470</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>45407</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>43993</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44655</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>46219</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>46267</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>46268</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46288</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>46126</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44929</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>46280</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45349</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45674</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>45656</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>44950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45228</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45212</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45681</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>44993</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>44812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45575</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45111</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>46290</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44714</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>45680</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46185</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46259</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>46126</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>46126</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>46126</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>45258</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>45343</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44593</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45244</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>45575</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>46085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>44859</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45674</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45546</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44942</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45257</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44645</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44476</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45313</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45629</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>45575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44676</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>44508</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>44859</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45447</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45503</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>46245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>46030</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45708</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44473</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>44874</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>44959</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45481</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44638</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45627</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44530</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44518</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44495</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44889</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44607</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44480</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44509</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44783</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44733</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44516</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>44844</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44607</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>44818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44647</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44487</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44510</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44753</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>44866</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44729</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44522</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44528</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44781</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44510</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44764</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44767</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44480</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44480</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44756</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44610</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44776</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44503</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44530</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44512</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44637</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44850</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44629</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44637</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44638</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44714</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44509</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44474</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>44637</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>44637</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>44486</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44796</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44514</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44641</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>44523</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44592</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44650</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44497</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44859</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44945</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45348</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44687</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45224</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45373</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45078</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44608</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44608</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44608</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45162</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44859</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>45517</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45307</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45667</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45343</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45741</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44497</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45817</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45617</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45035</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44631</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45569</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45656</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46010</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45453</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45453</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>46010</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44864</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>44950</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44474</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45817</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45254</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45897</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>46030</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>46030</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>46030</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>45208</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>44734</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45115</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45115</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45903</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46030</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46043</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>46042</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>46042</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45303</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46042</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45599</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45720</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45453</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45680</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45917</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45510</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45922</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>44487</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44866</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45572</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45072</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45930</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44967</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45936</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44928</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>46069</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46069</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45104</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44568</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45158</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>46071</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45170</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45027</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>44809</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45105</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>46080</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45000</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44593</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44558</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45964</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>45708</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45964</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45964</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46095</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45198</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45208</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45974</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>45484</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45089</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44828</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>44865</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>46112</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45502</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45471</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>46112</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>46112</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45986</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45825</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45987</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>46120</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45238</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45485</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45485</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45485</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44498</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>44662</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>44648</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>44739</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45994</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45733</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45642</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44855</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45072</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>46127</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44503</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45211</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45105</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45835</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45439</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>45827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45103</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45714</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44610</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45030</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>44606</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44812</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45072</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44511</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>46030</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>44959</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45975</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>45964</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45257</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45742</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45434</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45834</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44573</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>45253</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>44804</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45162</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>45937</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45469</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45933</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45254</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45107</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45608</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44970</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45904</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45599</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>44655</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45707</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>45587</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45391</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45364</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45303</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>45322</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46142</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>46142</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>46142</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>46142</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44573</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45327</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>44734</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45525</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45790</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44697</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45896</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>45964</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45441</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45303</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>46154</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>46157</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45246</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44662</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>46163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>46153</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>46163</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>46163</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45427</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44808</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>46007</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>46058</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44995</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>46170</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46170</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>46174</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>46174</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>46174</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>46174</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>46174</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45455</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>46171</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45373</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45404</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44676</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44909</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>44753</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>46181</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>46181</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>46181</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>46182</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>46176</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>46184</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44999</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>44999</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46184</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>46184</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>46185</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>45022</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46181</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>45609</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45533</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45408</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46185</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46189</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>46189</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>46189</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44957</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>46196</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45456</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>44494</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>46196</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>46196</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>46198</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32014,7 +32014,7 @@
         <v>44999</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32087,7 +32087,7 @@
         <v>46198</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>46198</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45301</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44578</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46184</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45115</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44889</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45226</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45664</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32749,7 +32749,7 @@
         <v>45664</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32822,7 +32822,7 @@
         <v>45162</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>46210</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>46210</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>46210</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>46210</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44748</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>44915</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>46216</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>46216</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>46258</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>45510</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>45473</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44739</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45042</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45525</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45285</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45481</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45217</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>46268</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44606</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>46268</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>45385</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>45132</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>46230</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>46230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>46230</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>44595</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>46230</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45104</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45104</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>46275</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>46275</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>46281</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>46237</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>44487</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>46230</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>46237</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>45572</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>46230</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>44907</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>46283</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>45495</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45469</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45511</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46287</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45190</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45235</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45391</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44615</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>44602</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45719</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>44791</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>46289</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>46289</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>46290</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45448</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46290</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45506</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>46290</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45191</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>46290</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>44517</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>44641</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>46290</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46290</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>44999</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>46252</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>46252</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>46252</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>44609</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>46297</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>46297</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>44950</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>44950</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46297</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45586</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38573,7 +38573,7 @@
         <v>45267</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>46297</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>46297</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>44488</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46297</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>46297</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>46254</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>44552</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>46297</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46297</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46297</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45511</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45327</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>44844</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>44995</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45184</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44487</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>44733</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>45481</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>44501</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>44642</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45007</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>45254</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>44497</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>44641</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45664</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45777</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45601</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>45559</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>45303</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45470</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>45407</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>43993</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>44655</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>46219</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>46267</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>46268</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46288</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44929</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45228</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45656</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45349</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44587</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45674</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>44950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>44812</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45681</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>44993</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45824</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45212</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>46290</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44714</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>45680</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>46281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>46259</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>44853</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44595</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45244</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>45313</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45104</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>45481</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45575</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>45503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>45525</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44942</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44593</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44959</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>44676</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45343</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44859</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45447</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44645</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45257</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45708</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>45629</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45030</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45674</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>46085</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>46245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>46030</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44638</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>45627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>44495</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>44530</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44606</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44480</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44509</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44783</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>44516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44844</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>44607</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>44647</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44510</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44753</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44866</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44729</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44528</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>44522</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>44781</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44510</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44637</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44637</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44509</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44637</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44486</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44530</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44637</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44733</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44512</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44767</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44764</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44480</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44480</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44831</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44638</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44850</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>44514</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>44714</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44756</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44641</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44629</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44610</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44509</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45238</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44592</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44650</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>44864</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45254</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45439</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45373</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45391</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44859</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45343</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45042</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45162</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45495</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45170</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45453</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>44809</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45391</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45572</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>44631</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>44791</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45224</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45455</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45469</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45115</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45115</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44608</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45089</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44501</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45104</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45211</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45664</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45664</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45434</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44503</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44497</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44957</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45208</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45481</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44907</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45715</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44739</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45664</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45533</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45484</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44950</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45254</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45609</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44487</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45525</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45708</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45104</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45817</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44558</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45078</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45817</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45897</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45235</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45427</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45586</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45473</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45481</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45253</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>44999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44999</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45903</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44999</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44915</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45608</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44642</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44494</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45303</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45777</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45599</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45511</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45303</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45559</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45601</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44552</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45470</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44995</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45572</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45667</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45917</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44866</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45407</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45922</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45348</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45190</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44608</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44608</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45569</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44615</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>44967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45132</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45103</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45327</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44950</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45617</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45510</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45930</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44568</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45720</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44578</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44676</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45408</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45587</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45385</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45104</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45680</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44593</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44602</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45404</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44662</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45303</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45198</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>44697</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>44606</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44641</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44641</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45217</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45072</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45191</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45162</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45198</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45115</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45027</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45226</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45267</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45825</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44609</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44498</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45642</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>44648</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45485</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45485</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44662</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>44855</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44739</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45733</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45485</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44828</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45456</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>44808</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44487</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45254</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45208</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45506</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45022</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45964</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44804</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45835</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45964</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45188</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44999</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45307</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45607</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45285</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45158</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44734</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45974</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45742</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45572</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45257</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45656</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45448</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44753</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44687</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>44748</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45471</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45719</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>46095</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45007</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45517</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45986</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45301</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45441</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>44889</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45511</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>44573</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45072</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45741</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45987</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45327</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44488</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45107</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44865</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>46112</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45453</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45453</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46112</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46112</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44595</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45105</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45525</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45994</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46120</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>44573</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>46127</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>46001</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>44610</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>44909</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>44928</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>44497</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45469</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44859</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44733</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45246</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45827</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45184</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>46010</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>46010</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45904</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>44959</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45072</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45937</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>44812</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46030</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45364</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>44511</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>46030</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46030</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>44487</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>45975</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44970</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45599</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44606</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44945</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45322</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44995</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45964</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45834</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>46030</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45035</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>46042</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>46042</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>46042</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>46030</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44655</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>46043</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>46045</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45933</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45030</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45373</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45714</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45707</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>46142</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44844</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45502</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>46142</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>46142</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>46142</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>44734</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>46069</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>46069</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>46071</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45964</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>46154</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>46080</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45896</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>45790</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45303</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>46157</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>46153</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>46163</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>46163</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>46163</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>46058</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46007</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>46170</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>46171</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>46170</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>46174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>46174</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34925,7 +34925,7 @@
         <v>46174</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>46174</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>46174</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46181</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>46181</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46181</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>46176</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>46184</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>46184</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>46184</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>46182</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>46185</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>46185</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>46185</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>46181</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>46189</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>46189</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>46189</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>46198</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>46196</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>46196</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>46196</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>46184</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>46198</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>46198</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>46210</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>46210</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>46210</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>46210</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>46216</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46216</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>46268</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>46268</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>46230</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>46230</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>46230</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>46230</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>46275</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>46275</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>46237</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>46237</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>46281</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>46230</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>46230</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>46283</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>46287</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>46289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38436,7 +38436,7 @@
         <v>46290</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>46290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>46290</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>46290</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>46290</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>46290</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>46289</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44517</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>46253</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>46252</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>46252</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46252</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>46297</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>46297</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46297</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>46297</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>46297</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>46254</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>46297</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>46297</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>46297</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>46297</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>46297</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>46258</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46303</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>43993</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44655</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>46219</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>46268</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>46267</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>46286</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>46288</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44929</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45228</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45656</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45349</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44587</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45674</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>44950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>44812</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45681</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>44993</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45824</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45212</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>45525</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>46290</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44714</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>44722</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>45680</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>46281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>46259</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>44853</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44595</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45244</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>45313</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45104</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>45481</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45575</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>45503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>45525</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44874</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44942</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44593</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44959</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>45258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>44676</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45343</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44859</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45447</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44645</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45257</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45708</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>45629</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45030</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45674</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>46085</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>46275</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>46245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>46030</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44638</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>45627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>44495</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>44530</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44606</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44480</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44509</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44783</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>44516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44844</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>44607</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>44647</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44510</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44753</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44866</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>44729</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44528</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>44522</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>44781</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44510</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44637</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44637</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44509</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44637</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44486</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44530</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44637</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44733</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44512</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44767</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44764</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44480</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44480</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44831</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44638</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44850</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>44514</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>44714</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44756</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44641</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44629</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44610</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44509</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45238</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44592</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44650</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>44864</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45254</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45439</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45373</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45391</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44859</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45343</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45042</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45162</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45495</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45170</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45453</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>44809</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45391</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45572</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>44631</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>44791</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45224</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45455</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45469</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45115</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45115</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44608</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45089</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44501</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45104</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45211</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45664</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45664</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45434</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44503</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44497</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44957</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45208</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45481</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44907</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45715</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44739</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45664</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45533</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45484</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44950</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44950</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45254</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45609</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44487</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45525</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45708</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45104</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45817</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44558</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45078</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45817</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45897</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45235</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45427</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45586</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45473</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45481</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45253</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>44999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44999</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45903</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44999</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44915</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45608</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44642</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44494</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45303</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45777</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45599</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45511</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45303</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45559</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45601</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44552</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45470</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>44995</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45572</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45667</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45917</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44866</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45407</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45922</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45348</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45190</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44608</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44608</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45569</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44615</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>44967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45132</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45103</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45327</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44950</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45617</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45510</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45930</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44568</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45720</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44578</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44676</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45408</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45587</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45385</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45104</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45680</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44593</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44602</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45404</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44662</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45303</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45198</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>44697</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>44606</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44641</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44641</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45217</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45072</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45191</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45162</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45198</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>45115</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>45027</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45226</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45267</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45825</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44609</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44498</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45642</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>44648</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45485</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45485</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44662</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>44855</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44739</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45733</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45485</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44828</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45456</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>44808</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44487</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45254</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45208</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45506</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45022</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45964</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>44804</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45835</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45964</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45188</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44999</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45307</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45607</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45285</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45158</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44734</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45974</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>45742</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45572</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45257</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45656</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45448</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44753</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44687</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>44748</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45471</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45719</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>46095</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45007</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45517</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45986</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45301</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45441</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>44889</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45511</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>44573</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45072</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45741</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45987</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45327</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44488</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45107</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44865</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>46112</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45453</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45453</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46112</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>46112</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44595</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45105</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45525</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45994</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46120</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>44573</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>46127</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>46001</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>44610</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>44909</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>44928</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>44497</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45469</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44859</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44733</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45246</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45827</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45184</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>46010</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>46010</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45904</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>44959</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45072</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45937</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>44812</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46030</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>45364</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>44511</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>46030</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46030</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30961,7 +30961,7 @@
         <v>44487</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>45975</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44970</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45599</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>44606</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44945</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45322</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>44995</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45964</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45834</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>46030</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45035</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>46042</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>46042</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>46042</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>46030</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>44655</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>46043</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>46045</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45933</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45030</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45373</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45714</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45707</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>46142</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44844</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45502</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>46142</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>46142</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>46142</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>44734</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>46069</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>46069</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>46071</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45964</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>46154</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>46080</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45896</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>45790</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45303</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>46157</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>46153</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>46163</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>46163</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>46163</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>46058</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46007</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>46170</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>46171</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>46170</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>46174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>46174</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34925,7 +34925,7 @@
         <v>46174</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>46174</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>46174</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46181</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>46181</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46181</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>46176</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>46184</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>46184</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>46184</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>46182</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>46185</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>46185</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>46185</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>46181</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>46189</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>46189</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>46189</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>46198</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>46196</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>46196</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>46196</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>46184</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>46198</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>46198</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>46210</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>46210</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>46210</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>46210</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>46216</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46216</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>46268</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>46268</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>46230</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>46230</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>46230</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>46230</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>46275</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>46275</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>46237</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>46237</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>46281</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>46230</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>46230</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>46283</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>46287</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>46289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38436,7 +38436,7 @@
         <v>46290</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>46290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>46290</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>46290</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>46290</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>46290</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>46289</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44517</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>46253</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>46252</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>46252</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>46252</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>46297</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>46297</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46297</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>46297</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>46297</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>46254</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>46297</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>46297</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>46297</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40044,7 +40044,7 @@
         <v>46297</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>46297</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>46258</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46303</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>43993</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>44655</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>46219</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>46268</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>46267</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>46286</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>46288</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44929</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45349</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45656</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>45228</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45674</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>44950</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45212</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44993</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>45810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45111</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>46290</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45681</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45824</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S 639-2023</t>
+          <t>S 1509-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44973</v>
+        <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4942,28 +4942,23 @@
           <t>ASKERSUND</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4981,1029 +4976,1040 @@
         <v>3</v>
       </c>
       <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Motaggsvamp
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/S 1509-2022 artfynd.xlsx", "S 1509-2022")</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/S 1509-2022 karta.png", "S 1509-2022")</f>
+        <v/>
+      </c>
+      <c r="Y39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/S 1509-2022 georefererad karta.tif", "S 1509-2022")</f>
+        <v/>
+      </c>
+      <c r="Z39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/knärot/S 1509-2022 karta knärot.png", "S 1509-2022")</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/S 1509-2022 FSC-klagomål.docx", "S 1509-2022")</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/S 1509-2022 FSC-klagomål mail.docx", "S 1509-2022")</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/S 1509-2022 tillsynsbegäran.docx", "S 1509-2022")</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/S 1509-2022 tillsynsbegäran mail.docx", "S 1509-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S 639-2023</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>44973</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
         <v>3</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>Ask
 Slåtterfibbla
 Blåsippa</t>
         </is>
       </c>
-      <c r="W39">
+      <c r="W40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/S 639-2023 artfynd.xlsx", "S 639-2023")</f>
         <v/>
       </c>
-      <c r="X39">
+      <c r="X40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/S 639-2023 karta.png", "S 639-2023")</f>
         <v/>
       </c>
-      <c r="Y39">
+      <c r="Y40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/S 639-2023 georefererad karta.tif", "S 639-2023")</f>
         <v/>
       </c>
-      <c r="AA39">
+      <c r="AA40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/S 639-2023 FSC-klagomål.docx", "S 639-2023")</f>
         <v/>
       </c>
-      <c r="AB39">
+      <c r="AB40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/S 639-2023 FSC-klagomål mail.docx", "S 639-2023")</f>
         <v/>
       </c>
-      <c r="AC39">
+      <c r="AC40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/S 639-2023 tillsynsbegäran.docx", "S 639-2023")</f>
         <v/>
       </c>
-      <c r="AD39">
+      <c r="AD40">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/S 639-2023 tillsynsbegäran mail.docx", "S 639-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>A 22787-2022</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="n">
         <v>44714</v>
       </c>
-      <c r="E40" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
+      <c r="E41" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
         <v>3.7</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>2</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T41" t="n">
         <v>2</v>
       </c>
-      <c r="U40" t="n">
+      <c r="U41" t="n">
         <v>2</v>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Revlummer</t>
         </is>
       </c>
-      <c r="W40">
+      <c r="W41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 22787-2022 artfynd.xlsx", "A 22787-2022")</f>
         <v/>
       </c>
-      <c r="X40">
+      <c r="X41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 22787-2022 karta.png", "A 22787-2022")</f>
         <v/>
       </c>
-      <c r="Y40">
+      <c r="Y41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 22787-2022 georefererad karta.tif", "A 22787-2022")</f>
         <v/>
       </c>
-      <c r="AA40">
+      <c r="AA41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 22787-2022 FSC-klagomål.docx", "A 22787-2022")</f>
         <v/>
       </c>
-      <c r="AB40">
+      <c r="AB41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 22787-2022 FSC-klagomål mail.docx", "A 22787-2022")</f>
         <v/>
       </c>
-      <c r="AC40">
+      <c r="AC41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 22787-2022 tillsynsbegäran.docx", "A 22787-2022")</f>
         <v/>
       </c>
-      <c r="AD40">
+      <c r="AD41">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 22787-2022 tillsynsbegäran mail.docx", "A 22787-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>A 3460-2025</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D42" s="1" t="n">
         <v>45680</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="E42" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="I42" t="n">
         <v>2.5</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
         <v>2</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T42" t="n">
         <v>2</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W41">
+      <c r="W42">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 3460-2025 artfynd.xlsx", "A 3460-2025")</f>
         <v/>
       </c>
-      <c r="X41">
+      <c r="X42">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 3460-2025 karta.png", "A 3460-2025")</f>
         <v/>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 3460-2025 georefererad karta.tif", "A 3460-2025")</f>
         <v/>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 3460-2025 FSC-klagomål.docx", "A 3460-2025")</f>
         <v/>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 3460-2025 FSC-klagomål mail.docx", "A 3460-2025")</f>
         <v/>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 3460-2025 tillsynsbegäran.docx", "A 3460-2025")</f>
         <v/>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 3460-2025 tillsynsbegäran mail.docx", "A 3460-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>A 25006-2026</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="E43" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="I43" t="n">
         <v>6.2</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>2</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T43" t="n">
         <v>2</v>
       </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Revlummer</t>
         </is>
       </c>
-      <c r="W42">
+      <c r="W43">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 25006-2026 artfynd.xlsx", "A 25006-2026")</f>
         <v/>
       </c>
-      <c r="X42">
+      <c r="X43">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 25006-2026 karta.png", "A 25006-2026")</f>
         <v/>
       </c>
-      <c r="Y42">
+      <c r="Y43">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 25006-2026 georefererad karta.tif", "A 25006-2026")</f>
         <v/>
       </c>
-      <c r="AA42">
+      <c r="AA43">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 25006-2026 FSC-klagomål.docx", "A 25006-2026")</f>
         <v/>
       </c>
-      <c r="AB42">
+      <c r="AB43">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 25006-2026 FSC-klagomål mail.docx", "A 25006-2026")</f>
         <v/>
       </c>
-      <c r="AC42">
+      <c r="AC43">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 25006-2026 tillsynsbegäran.docx", "A 25006-2026")</f>
         <v/>
       </c>
-      <c r="AD42">
+      <c r="AD43">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 25006-2026 tillsynsbegäran mail.docx", "A 25006-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>A 27023-2026</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
         <v>46185</v>
       </c>
-      <c r="E43" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="E44" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="I44" t="n">
         <v>2.3</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K44" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>2</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T44" t="n">
         <v>2</v>
       </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Blåsippa</t>
         </is>
       </c>
-      <c r="W43">
+      <c r="W44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 27023-2026 artfynd.xlsx", "A 27023-2026")</f>
         <v/>
       </c>
-      <c r="X43">
+      <c r="X44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 27023-2026 karta.png", "A 27023-2026")</f>
         <v/>
       </c>
-      <c r="Y43">
+      <c r="Y44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 27023-2026 georefererad karta.tif", "A 27023-2026")</f>
         <v/>
       </c>
-      <c r="AA43">
+      <c r="AA44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 27023-2026 FSC-klagomål.docx", "A 27023-2026")</f>
         <v/>
       </c>
-      <c r="AB43">
+      <c r="AB44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 27023-2026 FSC-klagomål mail.docx", "A 27023-2026")</f>
         <v/>
       </c>
-      <c r="AC43">
+      <c r="AC44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 27023-2026 tillsynsbegäran.docx", "A 27023-2026")</f>
         <v/>
       </c>
-      <c r="AD43">
+      <c r="AD44">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 27023-2026 tillsynsbegäran mail.docx", "A 27023-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>A 23750-2022</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
         <v>44722</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="E45" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I45" t="n">
         <v>4.3</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J45" t="n">
         <v>2</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
         <v>2</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T45" t="n">
         <v>3</v>
       </c>
-      <c r="U44" t="n">
+      <c r="U45" t="n">
         <v>3</v>
       </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Revlummer</t>
         </is>
       </c>
-      <c r="W44">
+      <c r="W45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 23750-2022 artfynd.xlsx", "A 23750-2022")</f>
         <v/>
       </c>
-      <c r="X44">
+      <c r="X45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 23750-2022 karta.png", "A 23750-2022")</f>
         <v/>
       </c>
-      <c r="Y44">
+      <c r="Y45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 23750-2022 georefererad karta.tif", "A 23750-2022")</f>
         <v/>
       </c>
-      <c r="AA44">
+      <c r="AA45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 23750-2022 FSC-klagomål.docx", "A 23750-2022")</f>
         <v/>
       </c>
-      <c r="AB44">
+      <c r="AB45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 23750-2022 FSC-klagomål mail.docx", "A 23750-2022")</f>
         <v/>
       </c>
-      <c r="AC44">
+      <c r="AC45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 23750-2022 tillsynsbegäran.docx", "A 23750-2022")</f>
         <v/>
       </c>
-      <c r="AD44">
+      <c r="AD45">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 23750-2022 tillsynsbegäran mail.docx", "A 23750-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>A 38246-2026</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="n">
         <v>46281</v>
       </c>
-      <c r="E45" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
+      <c r="E46" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
         <v>6.6</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K46" t="n">
         <v>1</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>2</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T46" t="n">
         <v>4</v>
       </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>Tibast
 Gullviva</t>
         </is>
       </c>
-      <c r="W45">
+      <c r="W46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 38246-2026 artfynd.xlsx", "A 38246-2026")</f>
         <v/>
       </c>
-      <c r="X45">
+      <c r="X46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 38246-2026 karta.png", "A 38246-2026")</f>
         <v/>
       </c>
-      <c r="Y45">
+      <c r="Y46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 38246-2026 georefererad karta.tif", "A 38246-2026")</f>
         <v/>
       </c>
-      <c r="AA45">
+      <c r="AA46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 38246-2026 FSC-klagomål.docx", "A 38246-2026")</f>
         <v/>
       </c>
-      <c r="AB45">
+      <c r="AB46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 38246-2026 FSC-klagomål mail.docx", "A 38246-2026")</f>
         <v/>
       </c>
-      <c r="AC45">
+      <c r="AC46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 38246-2026 tillsynsbegäran.docx", "A 38246-2026")</f>
         <v/>
       </c>
-      <c r="AD45">
+      <c r="AD46">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 38246-2026 tillsynsbegäran mail.docx", "A 38246-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>A 35059-2026</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="n">
         <v>46259</v>
       </c>
-      <c r="E46" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
+      <c r="E47" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>2</v>
       </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>2</v>
       </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>2</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T47" t="n">
         <v>2</v>
       </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>Ekticka
 Skogsklocka</t>
         </is>
       </c>
-      <c r="W46">
+      <c r="W47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 35059-2026 artfynd.xlsx", "A 35059-2026")</f>
         <v/>
       </c>
-      <c r="X46">
+      <c r="X47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 35059-2026 karta.png", "A 35059-2026")</f>
         <v/>
       </c>
-      <c r="Y46">
+      <c r="Y47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 35059-2026 georefererad karta.tif", "A 35059-2026")</f>
         <v/>
       </c>
-      <c r="AA46">
+      <c r="AA47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 35059-2026 FSC-klagomål.docx", "A 35059-2026")</f>
         <v/>
       </c>
-      <c r="AB46">
+      <c r="AB47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 35059-2026 FSC-klagomål mail.docx", "A 35059-2026")</f>
         <v/>
       </c>
-      <c r="AC46">
+      <c r="AC47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 35059-2026 tillsynsbegäran.docx", "A 35059-2026")</f>
         <v/>
       </c>
-      <c r="AD46">
+      <c r="AD47">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 35059-2026 tillsynsbegäran mail.docx", "A 35059-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>S 1741-2026</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D48" s="1" t="n">
         <v>46181</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="E48" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ASKERSUND</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="I48" t="n">
         <v>19.9</v>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>2</v>
       </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
         <v>2</v>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>2</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T48" t="n">
         <v>2</v>
       </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Svinrot</t>
         </is>
       </c>
-      <c r="W47">
+      <c r="W48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/S 1741-2026 artfynd.xlsx", "S 1741-2026")</f>
         <v/>
       </c>
-      <c r="X47">
+      <c r="X48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/S 1741-2026 karta.png", "S 1741-2026")</f>
         <v/>
       </c>
-      <c r="Y47">
+      <c r="Y48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/S 1741-2026 georefererad karta.tif", "S 1741-2026")</f>
         <v/>
       </c>
-      <c r="AA47">
+      <c r="AA48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/S 1741-2026 FSC-klagomål.docx", "S 1741-2026")</f>
         <v/>
       </c>
-      <c r="AB47">
+      <c r="AB48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/S 1741-2026 FSC-klagomål mail.docx", "S 1741-2026")</f>
         <v/>
       </c>
-      <c r="AC47">
+      <c r="AC48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/S 1741-2026 tillsynsbegäran.docx", "S 1741-2026")</f>
         <v/>
       </c>
-      <c r="AD47">
+      <c r="AD48">
         <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/S 1741-2026 tillsynsbegäran mail.docx", "S 1741-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>A 47371-2022</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>44853</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>ASKERSUND</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>9</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 47371-2022 artfynd.xlsx", "A 47371-2022")</f>
-        <v/>
-      </c>
-      <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 47371-2022 karta.png", "A 47371-2022")</f>
-        <v/>
-      </c>
-      <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 47371-2022 georefererad karta.tif", "A 47371-2022")</f>
-        <v/>
-      </c>
-      <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 47371-2022 FSC-klagomål.docx", "A 47371-2022")</f>
-        <v/>
-      </c>
-      <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 47371-2022 FSC-klagomål mail.docx", "A 47371-2022")</f>
-        <v/>
-      </c>
-      <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 47371-2022 tillsynsbegäran.docx", "A 47371-2022")</f>
-        <v/>
-      </c>
-      <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 47371-2022 tillsynsbegäran mail.docx", "A 47371-2022")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 66339-2021</t>
+          <t>A 47371-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6017,10 +6023,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44518</v>
+        <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6033,16 +6039,16 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -6057,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -6069,46 +6075,46 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 66339-2021 artfynd.xlsx", "A 66339-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 47371-2022 artfynd.xlsx", "A 47371-2022")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 66339-2021 karta.png", "A 66339-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 47371-2022 karta.png", "A 47371-2022")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 66339-2021 georefererad karta.tif", "A 66339-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 47371-2022 georefererad karta.tif", "A 47371-2022")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 66339-2021 FSC-klagomål.docx", "A 66339-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 47371-2022 FSC-klagomål.docx", "A 47371-2022")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 66339-2021 FSC-klagomål mail.docx", "A 66339-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 47371-2022 FSC-klagomål mail.docx", "A 47371-2022")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 66339-2021 tillsynsbegäran.docx", "A 66339-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 47371-2022 tillsynsbegäran.docx", "A 47371-2022")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 66339-2021 tillsynsbegäran mail.docx", "A 66339-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 47371-2022 tillsynsbegäran mail.docx", "A 47371-2022")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5504-2022</t>
+          <t>A 66339-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6122,10 +6128,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44595</v>
+        <v>44518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6138,17 +6144,17 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
@@ -6162,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -6174,46 +6180,46 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 5504-2022 artfynd.xlsx", "A 5504-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 66339-2021 artfynd.xlsx", "A 66339-2021")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 5504-2022 karta.png", "A 5504-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 66339-2021 karta.png", "A 66339-2021")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 5504-2022 georefererad karta.tif", "A 5504-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 66339-2021 georefererad karta.tif", "A 66339-2021")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 5504-2022 FSC-klagomål.docx", "A 5504-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 66339-2021 FSC-klagomål.docx", "A 66339-2021")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 5504-2022 FSC-klagomål mail.docx", "A 5504-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 66339-2021 FSC-klagomål mail.docx", "A 66339-2021")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 5504-2022 tillsynsbegäran.docx", "A 5504-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 66339-2021 tillsynsbegäran.docx", "A 66339-2021")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 5504-2022 tillsynsbegäran mail.docx", "A 5504-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 66339-2021 tillsynsbegäran mail.docx", "A 66339-2021")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 63422-2021</t>
+          <t>A 5504-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6227,10 +6233,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44508</v>
+        <v>44595</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6243,16 +6249,16 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -6267,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -6279,46 +6285,46 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Humlerotfjäril</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 63422-2021 artfynd.xlsx", "A 63422-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 5504-2022 artfynd.xlsx", "A 5504-2022")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 63422-2021 karta.png", "A 63422-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 5504-2022 karta.png", "A 5504-2022")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 63422-2021 georefererad karta.tif", "A 63422-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 5504-2022 georefererad karta.tif", "A 5504-2022")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 63422-2021 FSC-klagomål.docx", "A 63422-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 5504-2022 FSC-klagomål.docx", "A 5504-2022")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 63422-2021 FSC-klagomål mail.docx", "A 63422-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 5504-2022 FSC-klagomål mail.docx", "A 5504-2022")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 63422-2021 tillsynsbegäran.docx", "A 63422-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 5504-2022 tillsynsbegäran.docx", "A 5504-2022")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 63422-2021 tillsynsbegäran mail.docx", "A 63422-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 5504-2022 tillsynsbegäran mail.docx", "A 5504-2022")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5044-2022</t>
+          <t>A 63422-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6332,10 +6338,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44593</v>
+        <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6347,13 +6353,8 @@
           <t>ASKERSUND</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6389,46 +6390,46 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Humlerotfjäril</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 5044-2022 artfynd.xlsx", "A 5044-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 63422-2021 artfynd.xlsx", "A 63422-2021")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 5044-2022 karta.png", "A 5044-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 63422-2021 karta.png", "A 63422-2021")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 5044-2022 georefererad karta.tif", "A 5044-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 63422-2021 georefererad karta.tif", "A 63422-2021")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 5044-2022 FSC-klagomål.docx", "A 5044-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 63422-2021 FSC-klagomål.docx", "A 63422-2021")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 5044-2022 FSC-klagomål mail.docx", "A 5044-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 63422-2021 FSC-klagomål mail.docx", "A 63422-2021")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 5044-2022 tillsynsbegäran.docx", "A 5044-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 63422-2021 tillsynsbegäran.docx", "A 63422-2021")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 5044-2022 tillsynsbegäran mail.docx", "A 5044-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 63422-2021 tillsynsbegäran mail.docx", "A 63422-2021")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56967-2023</t>
+          <t>A 5044-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6442,10 +6443,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45244</v>
+        <v>44593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6459,11 +6460,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6503,42 +6504,42 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 56967-2023 artfynd.xlsx", "A 56967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 5044-2022 artfynd.xlsx", "A 5044-2022")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 56967-2023 karta.png", "A 56967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 5044-2022 karta.png", "A 5044-2022")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 56967-2023 georefererad karta.tif", "A 56967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 5044-2022 georefererad karta.tif", "A 5044-2022")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 56967-2023 FSC-klagomål.docx", "A 56967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 5044-2022 FSC-klagomål.docx", "A 5044-2022")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 56967-2023 FSC-klagomål mail.docx", "A 56967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 5044-2022 FSC-klagomål mail.docx", "A 5044-2022")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 56967-2023 tillsynsbegäran.docx", "A 56967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 5044-2022 tillsynsbegäran.docx", "A 5044-2022")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 56967-2023 tillsynsbegäran mail.docx", "A 56967-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 5044-2022 tillsynsbegäran mail.docx", "A 5044-2022")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 44888-2024</t>
+          <t>A 56967-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6548,14 +6549,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45575</v>
+        <v>45244</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6573,17 +6574,17 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
@@ -6597,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -6613,42 +6614,42 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 44888-2024 artfynd.xlsx", "A 44888-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 56967-2023 artfynd.xlsx", "A 56967-2023")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 44888-2024 karta.png", "A 44888-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 56967-2023 karta.png", "A 56967-2023")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 44888-2024 georefererad karta.tif", "A 44888-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 56967-2023 georefererad karta.tif", "A 56967-2023")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 44888-2024 FSC-klagomål.docx", "A 44888-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 56967-2023 FSC-klagomål.docx", "A 56967-2023")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 44888-2024 FSC-klagomål mail.docx", "A 44888-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 56967-2023 FSC-klagomål mail.docx", "A 56967-2023")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 44888-2024 tillsynsbegäran.docx", "A 44888-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 56967-2023 tillsynsbegäran.docx", "A 56967-2023")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 44888-2024 tillsynsbegäran mail.docx", "A 44888-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 56967-2023 tillsynsbegäran mail.docx", "A 56967-2023")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48884-2022</t>
+          <t>A 44888-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6658,14 +6659,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44859</v>
+        <v>45575</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6677,17 +6678,22 @@
           <t>ASKERSUND</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6702,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -6718,42 +6724,42 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 48884-2022 artfynd.xlsx", "A 48884-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 44888-2024 artfynd.xlsx", "A 44888-2024")</f>
         <v/>
       </c>
       <c r="X55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 48884-2022 karta.png", "A 48884-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 44888-2024 karta.png", "A 44888-2024")</f>
         <v/>
       </c>
       <c r="Y55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 48884-2022 georefererad karta.tif", "A 48884-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 44888-2024 georefererad karta.tif", "A 44888-2024")</f>
         <v/>
       </c>
       <c r="AA55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 48884-2022 FSC-klagomål.docx", "A 48884-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 44888-2024 FSC-klagomål.docx", "A 44888-2024")</f>
         <v/>
       </c>
       <c r="AB55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 48884-2022 FSC-klagomål mail.docx", "A 48884-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 44888-2024 FSC-klagomål mail.docx", "A 44888-2024")</f>
         <v/>
       </c>
       <c r="AC55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 48884-2022 tillsynsbegäran.docx", "A 48884-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 44888-2024 tillsynsbegäran.docx", "A 44888-2024")</f>
         <v/>
       </c>
       <c r="AD55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 48884-2022 tillsynsbegäran mail.docx", "A 48884-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 44888-2024 tillsynsbegäran mail.docx", "A 44888-2024")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16677-2023</t>
+          <t>A 48884-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6767,10 +6773,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45030</v>
+        <v>44859</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6783,17 +6789,17 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
         <v>1</v>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
@@ -6807,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -6823,42 +6829,42 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 16677-2023 artfynd.xlsx", "A 16677-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 48884-2022 artfynd.xlsx", "A 48884-2022")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 16677-2023 karta.png", "A 16677-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 48884-2022 karta.png", "A 48884-2022")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 16677-2023 georefererad karta.tif", "A 16677-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 48884-2022 georefererad karta.tif", "A 48884-2022")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 16677-2023 FSC-klagomål.docx", "A 16677-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 48884-2022 FSC-klagomål.docx", "A 48884-2022")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 16677-2023 FSC-klagomål mail.docx", "A 16677-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 48884-2022 FSC-klagomål mail.docx", "A 48884-2022")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 16677-2023 tillsynsbegäran.docx", "A 16677-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 48884-2022 tillsynsbegäran.docx", "A 48884-2022")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 16677-2023 tillsynsbegäran mail.docx", "A 16677-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 48884-2022 tillsynsbegäran mail.docx", "A 48884-2022")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2445-2025</t>
+          <t>A 16677-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6872,10 +6878,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45674</v>
+        <v>45030</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6888,16 +6894,16 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6912,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -6928,42 +6934,42 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Åkerväddsantennmal</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 2445-2025 artfynd.xlsx", "A 2445-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 16677-2023 artfynd.xlsx", "A 16677-2023")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 2445-2025 karta.png", "A 2445-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 16677-2023 karta.png", "A 16677-2023")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 2445-2025 georefererad karta.tif", "A 2445-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 16677-2023 georefererad karta.tif", "A 16677-2023")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 2445-2025 FSC-klagomål.docx", "A 2445-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 16677-2023 FSC-klagomål.docx", "A 16677-2023")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 2445-2025 FSC-klagomål mail.docx", "A 2445-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 16677-2023 FSC-klagomål mail.docx", "A 16677-2023")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 2445-2025 tillsynsbegäran.docx", "A 2445-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 16677-2023 tillsynsbegäran.docx", "A 16677-2023")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 2445-2025 tillsynsbegäran mail.docx", "A 2445-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 16677-2023 tillsynsbegäran mail.docx", "A 16677-2023")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38601-2024</t>
+          <t>A 2445-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6977,10 +6983,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45546</v>
+        <v>45674</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6992,13 +6998,8 @@
           <t>ASKERSUND</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7034,46 +7035,46 @@
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Åkerväddsantennmal</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 38601-2024 artfynd.xlsx", "A 38601-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 2445-2025 artfynd.xlsx", "A 2445-2025")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 38601-2024 karta.png", "A 38601-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 2445-2025 karta.png", "A 2445-2025")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 38601-2024 georefererad karta.tif", "A 38601-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 2445-2025 georefererad karta.tif", "A 2445-2025")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 38601-2024 FSC-klagomål.docx", "A 38601-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 2445-2025 FSC-klagomål.docx", "A 2445-2025")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 38601-2024 FSC-klagomål mail.docx", "A 38601-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 2445-2025 FSC-klagomål mail.docx", "A 2445-2025")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 38601-2024 tillsynsbegäran.docx", "A 38601-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 2445-2025 tillsynsbegäran.docx", "A 2445-2025")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 38601-2024 tillsynsbegäran mail.docx", "A 38601-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 2445-2025 tillsynsbegäran mail.docx", "A 2445-2025")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2295-2023</t>
+          <t>A 38601-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7087,10 +7088,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44942</v>
+        <v>45546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,11 +7103,16 @@
           <t>ASKERSUND</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -7143,46 +7149,42 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 2295-2023 artfynd.xlsx", "A 2295-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 38601-2024 artfynd.xlsx", "A 38601-2024")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 2295-2023 karta.png", "A 2295-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 38601-2024 karta.png", "A 38601-2024")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 2295-2023 georefererad karta.tif", "A 2295-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 38601-2024 georefererad karta.tif", "A 38601-2024")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 2295-2023 FSC-klagomål.docx", "A 2295-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 38601-2024 FSC-klagomål.docx", "A 38601-2024")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 2295-2023 FSC-klagomål mail.docx", "A 2295-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 38601-2024 FSC-klagomål mail.docx", "A 38601-2024")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 2295-2023 tillsynsbegäran.docx", "A 2295-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 38601-2024 tillsynsbegäran.docx", "A 38601-2024")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 2295-2023 tillsynsbegäran mail.docx", "A 2295-2023")</f>
-        <v/>
-      </c>
-      <c r="AE59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/fåglar/A 2295-2023 prioriterade fågelarter.docx", "A 2295-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 38601-2024 tillsynsbegäran mail.docx", "A 38601-2024")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32037-2024</t>
+          <t>A 2295-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7196,10 +7198,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45510</v>
+        <v>44942</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7212,17 +7214,17 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
         <v>1</v>
       </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
@@ -7236,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -7248,46 +7250,50 @@
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="W60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 32037-2024 artfynd.xlsx", "A 32037-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 2295-2023 artfynd.xlsx", "A 2295-2023")</f>
         <v/>
       </c>
       <c r="X60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 32037-2024 karta.png", "A 32037-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 2295-2023 karta.png", "A 2295-2023")</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 32037-2024 georefererad karta.tif", "A 32037-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 2295-2023 georefererad karta.tif", "A 2295-2023")</f>
         <v/>
       </c>
       <c r="AA60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 32037-2024 FSC-klagomål.docx", "A 32037-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 2295-2023 FSC-klagomål.docx", "A 2295-2023")</f>
         <v/>
       </c>
       <c r="AB60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 32037-2024 FSC-klagomål mail.docx", "A 32037-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 2295-2023 FSC-klagomål mail.docx", "A 2295-2023")</f>
         <v/>
       </c>
       <c r="AC60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 32037-2024 tillsynsbegäran.docx", "A 32037-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 2295-2023 tillsynsbegäran.docx", "A 2295-2023")</f>
         <v/>
       </c>
       <c r="AD60">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 32037-2024 tillsynsbegäran mail.docx", "A 32037-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 2295-2023 tillsynsbegäran mail.docx", "A 2295-2023")</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/fåglar/A 2295-2023 prioriterade fågelarter.docx", "A 2295-2023")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34514-2024</t>
+          <t>A 32037-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7297,14 +7303,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45525</v>
+        <v>45510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7316,19 +7322,14 @@
           <t>ASKERSUND</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7362,42 +7363,42 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 34514-2024 artfynd.xlsx", "A 34514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 32037-2024 artfynd.xlsx", "A 32037-2024")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 34514-2024 karta.png", "A 34514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 32037-2024 karta.png", "A 32037-2024")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 34514-2024 georefererad karta.tif", "A 34514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 32037-2024 georefererad karta.tif", "A 32037-2024")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 34514-2024 FSC-klagomål.docx", "A 34514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 32037-2024 FSC-klagomål.docx", "A 32037-2024")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 34514-2024 FSC-klagomål mail.docx", "A 34514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 32037-2024 FSC-klagomål mail.docx", "A 32037-2024")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 34514-2024 tillsynsbegäran.docx", "A 34514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 32037-2024 tillsynsbegäran.docx", "A 32037-2024")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 34514-2024 tillsynsbegäran mail.docx", "A 34514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 32037-2024 tillsynsbegäran mail.docx", "A 32037-2024")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2561-2024</t>
+          <t>A 34514-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7407,14 +7408,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45313</v>
+        <v>45525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7426,11 +7427,16 @@
           <t>ASKERSUND</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -7439,7 +7445,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -7451,10 +7457,10 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7463,46 +7469,46 @@
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 2561-2024 artfynd.xlsx", "A 2561-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 34514-2024 artfynd.xlsx", "A 34514-2024")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 2561-2024 karta.png", "A 2561-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 34514-2024 karta.png", "A 34514-2024")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 2561-2024 georefererad karta.tif", "A 2561-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 34514-2024 georefererad karta.tif", "A 34514-2024")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 2561-2024 FSC-klagomål.docx", "A 2561-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 34514-2024 FSC-klagomål.docx", "A 34514-2024")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 2561-2024 FSC-klagomål mail.docx", "A 2561-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 34514-2024 FSC-klagomål mail.docx", "A 34514-2024")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 2561-2024 tillsynsbegäran.docx", "A 2561-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 34514-2024 tillsynsbegäran.docx", "A 34514-2024")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 2561-2024 tillsynsbegäran mail.docx", "A 2561-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 34514-2024 tillsynsbegäran mail.docx", "A 34514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57427-2024</t>
+          <t>A 2561-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7516,10 +7522,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45629</v>
+        <v>45313</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7532,20 +7538,20 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>1</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
@@ -7556,58 +7562,58 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 57427-2024 artfynd.xlsx", "A 57427-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 2561-2024 artfynd.xlsx", "A 2561-2024")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 57427-2024 karta.png", "A 57427-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 2561-2024 karta.png", "A 2561-2024")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 57427-2024 georefererad karta.tif", "A 57427-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 2561-2024 georefererad karta.tif", "A 2561-2024")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 57427-2024 FSC-klagomål.docx", "A 57427-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 2561-2024 FSC-klagomål.docx", "A 2561-2024")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 57427-2024 FSC-klagomål mail.docx", "A 57427-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 2561-2024 FSC-klagomål mail.docx", "A 2561-2024")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 57427-2024 tillsynsbegäran.docx", "A 57427-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 2561-2024 tillsynsbegäran.docx", "A 2561-2024")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 57427-2024 tillsynsbegäran mail.docx", "A 57427-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 2561-2024 tillsynsbegäran mail.docx", "A 2561-2024")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28786-2023</t>
+          <t>A 57427-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7617,14 +7623,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45104</v>
+        <v>45629</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7637,13 +7643,13 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7670,49 +7676,49 @@
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 28786-2023 artfynd.xlsx", "A 28786-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 57427-2024 artfynd.xlsx", "A 57427-2024")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 28786-2023 karta.png", "A 28786-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 57427-2024 karta.png", "A 57427-2024")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 28786-2023 georefererad karta.tif", "A 28786-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 57427-2024 georefererad karta.tif", "A 57427-2024")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 28786-2023 FSC-klagomål.docx", "A 28786-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 57427-2024 FSC-klagomål.docx", "A 57427-2024")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 28786-2023 FSC-klagomål mail.docx", "A 28786-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 57427-2024 FSC-klagomål mail.docx", "A 57427-2024")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 28786-2023 tillsynsbegäran.docx", "A 28786-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 57427-2024 tillsynsbegäran.docx", "A 57427-2024")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 28786-2023 tillsynsbegäran mail.docx", "A 28786-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 57427-2024 tillsynsbegäran mail.docx", "A 57427-2024")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44891-2024</t>
+          <t>A 28786-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7722,14 +7728,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45575</v>
+        <v>45104</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7741,19 +7747,14 @@
           <t>ASKERSUND</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
         <v>1</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7787,42 +7788,42 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 44891-2024 artfynd.xlsx", "A 44891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 28786-2023 artfynd.xlsx", "A 28786-2023")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 44891-2024 karta.png", "A 44891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 28786-2023 karta.png", "A 28786-2023")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 44891-2024 georefererad karta.tif", "A 44891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 28786-2023 georefererad karta.tif", "A 28786-2023")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 44891-2024 FSC-klagomål.docx", "A 44891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 28786-2023 FSC-klagomål.docx", "A 28786-2023")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 44891-2024 FSC-klagomål mail.docx", "A 44891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 28786-2023 FSC-klagomål mail.docx", "A 28786-2023")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 44891-2024 tillsynsbegäran.docx", "A 44891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 28786-2023 tillsynsbegäran.docx", "A 28786-2023")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 44891-2024 tillsynsbegäran mail.docx", "A 44891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 28786-2023 tillsynsbegäran mail.docx", "A 28786-2023")</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16953-2022</t>
+          <t>A 44891-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7832,14 +7833,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44676</v>
+        <v>45575</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7851,8 +7852,13 @@
           <t>ASKERSUND</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -7861,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -7876,7 +7882,7 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -7888,50 +7894,46 @@
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 16953-2022 artfynd.xlsx", "A 16953-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 44891-2024 artfynd.xlsx", "A 44891-2024")</f>
         <v/>
       </c>
       <c r="X66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 16953-2022 karta.png", "A 16953-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 44891-2024 karta.png", "A 44891-2024")</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 16953-2022 georefererad karta.tif", "A 16953-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 44891-2024 georefererad karta.tif", "A 44891-2024")</f>
         <v/>
       </c>
       <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 16953-2022 FSC-klagomål.docx", "A 16953-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 44891-2024 FSC-klagomål.docx", "A 44891-2024")</f>
         <v/>
       </c>
       <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 16953-2022 FSC-klagomål mail.docx", "A 16953-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 44891-2024 FSC-klagomål mail.docx", "A 44891-2024")</f>
         <v/>
       </c>
       <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 16953-2022 tillsynsbegäran.docx", "A 16953-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 44891-2024 tillsynsbegäran.docx", "A 44891-2024")</f>
         <v/>
       </c>
       <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 16953-2022 tillsynsbegäran mail.docx", "A 16953-2022")</f>
-        <v/>
-      </c>
-      <c r="AE66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/fåglar/A 16953-2022 prioriterade fågelarter.docx", "A 16953-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 44891-2024 tillsynsbegäran mail.docx", "A 44891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 63535-2021</t>
+          <t>A 16953-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7945,10 +7947,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44508</v>
+        <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7961,10 +7963,10 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -8001,42 +8003,46 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Humlerotfjäril</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 63535-2021 artfynd.xlsx", "A 63535-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 16953-2022 artfynd.xlsx", "A 16953-2022")</f>
         <v/>
       </c>
       <c r="X67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 63535-2021 karta.png", "A 63535-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 16953-2022 karta.png", "A 16953-2022")</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 63535-2021 georefererad karta.tif", "A 63535-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 16953-2022 georefererad karta.tif", "A 16953-2022")</f>
         <v/>
       </c>
       <c r="AA67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 63535-2021 FSC-klagomål.docx", "A 63535-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 16953-2022 FSC-klagomål.docx", "A 16953-2022")</f>
         <v/>
       </c>
       <c r="AB67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 63535-2021 FSC-klagomål mail.docx", "A 63535-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 16953-2022 FSC-klagomål mail.docx", "A 16953-2022")</f>
         <v/>
       </c>
       <c r="AC67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 63535-2021 tillsynsbegäran.docx", "A 63535-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 16953-2022 tillsynsbegäran.docx", "A 16953-2022")</f>
         <v/>
       </c>
       <c r="AD67">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 63535-2021 tillsynsbegäran mail.docx", "A 63535-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 16953-2022 tillsynsbegäran mail.docx", "A 16953-2022")</f>
+        <v/>
+      </c>
+      <c r="AE67">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/fåglar/A 16953-2022 prioriterade fågelarter.docx", "A 16953-2022")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48879-2022</t>
+          <t>A 63535-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8050,10 +8056,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44859</v>
+        <v>44508</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8066,7 +8072,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -8075,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -8090,7 +8096,7 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -8106,42 +8112,42 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Humlerotfjäril</t>
         </is>
       </c>
       <c r="W68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 48879-2022 artfynd.xlsx", "A 48879-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 63535-2021 artfynd.xlsx", "A 63535-2021")</f>
         <v/>
       </c>
       <c r="X68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 48879-2022 karta.png", "A 48879-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 63535-2021 karta.png", "A 63535-2021")</f>
         <v/>
       </c>
       <c r="Y68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 48879-2022 georefererad karta.tif", "A 48879-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 63535-2021 georefererad karta.tif", "A 63535-2021")</f>
         <v/>
       </c>
       <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 48879-2022 FSC-klagomål.docx", "A 48879-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 63535-2021 FSC-klagomål.docx", "A 63535-2021")</f>
         <v/>
       </c>
       <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 48879-2022 FSC-klagomål mail.docx", "A 48879-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 63535-2021 FSC-klagomål mail.docx", "A 63535-2021")</f>
         <v/>
       </c>
       <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 48879-2022 tillsynsbegäran.docx", "A 48879-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 63535-2021 tillsynsbegäran.docx", "A 63535-2021")</f>
         <v/>
       </c>
       <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 48879-2022 tillsynsbegäran mail.docx", "A 48879-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 63535-2021 tillsynsbegäran mail.docx", "A 63535-2021")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11988-2026</t>
+          <t>A 48879-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8151,14 +8157,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46085</v>
+        <v>44859</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8171,13 +8177,13 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -8211,42 +8217,42 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="W69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 11988-2026 artfynd.xlsx", "A 11988-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 48879-2022 artfynd.xlsx", "A 48879-2022")</f>
         <v/>
       </c>
       <c r="X69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 11988-2026 karta.png", "A 11988-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 48879-2022 karta.png", "A 48879-2022")</f>
         <v/>
       </c>
       <c r="Y69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 11988-2026 georefererad karta.tif", "A 11988-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 48879-2022 georefererad karta.tif", "A 48879-2022")</f>
         <v/>
       </c>
       <c r="AA69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 11988-2026 FSC-klagomål.docx", "A 11988-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 48879-2022 FSC-klagomål.docx", "A 48879-2022")</f>
         <v/>
       </c>
       <c r="AB69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 11988-2026 FSC-klagomål mail.docx", "A 11988-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 48879-2022 FSC-klagomål mail.docx", "A 48879-2022")</f>
         <v/>
       </c>
       <c r="AC69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 11988-2026 tillsynsbegäran.docx", "A 11988-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 48879-2022 tillsynsbegäran.docx", "A 48879-2022")</f>
         <v/>
       </c>
       <c r="AD69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 11988-2026 tillsynsbegäran mail.docx", "A 11988-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 48879-2022 tillsynsbegäran mail.docx", "A 48879-2022")</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22511-2024</t>
+          <t>A 11988-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8256,14 +8262,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45447</v>
+        <v>46085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8282,10 +8288,10 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -8300,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -8312,46 +8318,46 @@
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 22511-2024 artfynd.xlsx", "A 22511-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 11988-2026 artfynd.xlsx", "A 11988-2026")</f>
         <v/>
       </c>
       <c r="X70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 22511-2024 karta.png", "A 22511-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 11988-2026 karta.png", "A 11988-2026")</f>
         <v/>
       </c>
       <c r="Y70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 22511-2024 georefererad karta.tif", "A 22511-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 11988-2026 georefererad karta.tif", "A 11988-2026")</f>
         <v/>
       </c>
       <c r="AA70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 22511-2024 FSC-klagomål.docx", "A 22511-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 11988-2026 FSC-klagomål.docx", "A 11988-2026")</f>
         <v/>
       </c>
       <c r="AB70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 22511-2024 FSC-klagomål mail.docx", "A 22511-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 11988-2026 FSC-klagomål mail.docx", "A 11988-2026")</f>
         <v/>
       </c>
       <c r="AC70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 22511-2024 tillsynsbegäran.docx", "A 22511-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 11988-2026 tillsynsbegäran.docx", "A 11988-2026")</f>
         <v/>
       </c>
       <c r="AD70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 22511-2024 tillsynsbegäran mail.docx", "A 22511-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 11988-2026 tillsynsbegäran mail.docx", "A 11988-2026")</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31265-2024</t>
+          <t>A 22511-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8365,10 +8371,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45503</v>
+        <v>45447</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8381,17 +8387,17 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>15.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
@@ -8405,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -8417,50 +8423,46 @@
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 31265-2024 artfynd.xlsx", "A 31265-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 22511-2024 artfynd.xlsx", "A 22511-2024")</f>
         <v/>
       </c>
       <c r="X71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 31265-2024 karta.png", "A 31265-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 22511-2024 karta.png", "A 22511-2024")</f>
         <v/>
       </c>
       <c r="Y71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 31265-2024 georefererad karta.tif", "A 31265-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 22511-2024 georefererad karta.tif", "A 22511-2024")</f>
         <v/>
       </c>
       <c r="AA71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 31265-2024 FSC-klagomål.docx", "A 31265-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 22511-2024 FSC-klagomål.docx", "A 22511-2024")</f>
         <v/>
       </c>
       <c r="AB71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 31265-2024 FSC-klagomål mail.docx", "A 31265-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 22511-2024 FSC-klagomål mail.docx", "A 22511-2024")</f>
         <v/>
       </c>
       <c r="AC71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 31265-2024 tillsynsbegäran.docx", "A 31265-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 22511-2024 tillsynsbegäran.docx", "A 22511-2024")</f>
         <v/>
       </c>
       <c r="AD71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 31265-2024 tillsynsbegäran mail.docx", "A 31265-2024")</f>
-        <v/>
-      </c>
-      <c r="AE71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/fåglar/A 31265-2024 prioriterade fågelarter.docx", "A 31265-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 22511-2024 tillsynsbegäran mail.docx", "A 22511-2024")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37442-2026</t>
+          <t>A 31265-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8474,10 +8476,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46275</v>
+        <v>45503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8489,13 +8491,8 @@
           <t>ASKERSUND</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>15.5</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -8531,46 +8528,50 @@
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="W72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 37442-2026 artfynd.xlsx", "A 37442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 31265-2024 artfynd.xlsx", "A 31265-2024")</f>
         <v/>
       </c>
       <c r="X72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 37442-2026 karta.png", "A 37442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 31265-2024 karta.png", "A 31265-2024")</f>
         <v/>
       </c>
       <c r="Y72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 37442-2026 georefererad karta.tif", "A 37442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 31265-2024 georefererad karta.tif", "A 31265-2024")</f>
         <v/>
       </c>
       <c r="AA72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 37442-2026 FSC-klagomål.docx", "A 37442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 31265-2024 FSC-klagomål.docx", "A 31265-2024")</f>
         <v/>
       </c>
       <c r="AB72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 37442-2026 FSC-klagomål mail.docx", "A 37442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 31265-2024 FSC-klagomål mail.docx", "A 31265-2024")</f>
         <v/>
       </c>
       <c r="AC72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 37442-2026 tillsynsbegäran.docx", "A 37442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 31265-2024 tillsynsbegäran.docx", "A 31265-2024")</f>
         <v/>
       </c>
       <c r="AD72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 37442-2026 tillsynsbegäran mail.docx", "A 37442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 31265-2024 tillsynsbegäran mail.docx", "A 31265-2024")</f>
+        <v/>
+      </c>
+      <c r="AE72">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/fåglar/A 31265-2024 prioriterade fågelarter.docx", "A 31265-2024")</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8366-2025</t>
+          <t>A 37442-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8584,10 +8585,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45708</v>
+        <v>46275</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8599,8 +8600,13 @@
           <t>ASKERSUND</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>1</v>
@@ -8640,42 +8646,42 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 8366-2025 artfynd.xlsx", "A 8366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 37442-2026 artfynd.xlsx", "A 37442-2026")</f>
         <v/>
       </c>
       <c r="X73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 8366-2025 karta.png", "A 8366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 37442-2026 karta.png", "A 37442-2026")</f>
         <v/>
       </c>
       <c r="Y73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 8366-2025 georefererad karta.tif", "A 8366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 37442-2026 georefererad karta.tif", "A 37442-2026")</f>
         <v/>
       </c>
       <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 8366-2025 FSC-klagomål.docx", "A 8366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 37442-2026 FSC-klagomål.docx", "A 37442-2026")</f>
         <v/>
       </c>
       <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 8366-2025 FSC-klagomål mail.docx", "A 8366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 37442-2026 FSC-klagomål mail.docx", "A 37442-2026")</f>
         <v/>
       </c>
       <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 8366-2025 tillsynsbegäran.docx", "A 8366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 37442-2026 tillsynsbegäran.docx", "A 37442-2026")</f>
         <v/>
       </c>
       <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 8366-2025 tillsynsbegäran mail.docx", "A 8366-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 37442-2026 tillsynsbegäran mail.docx", "A 37442-2026")</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52518-2022</t>
+          <t>A 8366-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8689,10 +8695,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44874</v>
+        <v>45708</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8705,13 +8711,13 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -8745,42 +8751,42 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 52518-2022 artfynd.xlsx", "A 52518-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 8366-2025 artfynd.xlsx", "A 8366-2025")</f>
         <v/>
       </c>
       <c r="X74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 52518-2022 karta.png", "A 52518-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 8366-2025 karta.png", "A 8366-2025")</f>
         <v/>
       </c>
       <c r="Y74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 52518-2022 georefererad karta.tif", "A 52518-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 8366-2025 georefererad karta.tif", "A 8366-2025")</f>
         <v/>
       </c>
       <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 52518-2022 FSC-klagomål.docx", "A 52518-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 8366-2025 FSC-klagomål.docx", "A 8366-2025")</f>
         <v/>
       </c>
       <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 52518-2022 FSC-klagomål mail.docx", "A 52518-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 8366-2025 FSC-klagomål mail.docx", "A 8366-2025")</f>
         <v/>
       </c>
       <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 52518-2022 tillsynsbegäran.docx", "A 52518-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 8366-2025 tillsynsbegäran.docx", "A 8366-2025")</f>
         <v/>
       </c>
       <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 52518-2022 tillsynsbegäran mail.docx", "A 52518-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 8366-2025 tillsynsbegäran mail.docx", "A 8366-2025")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 33113-2026</t>
+          <t>A 52518-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8794,10 +8800,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46245</v>
+        <v>44874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8810,13 +8816,13 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
         <v>1</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -8850,42 +8856,42 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 33113-2026 artfynd.xlsx", "A 33113-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 52518-2022 artfynd.xlsx", "A 52518-2022")</f>
         <v/>
       </c>
       <c r="X75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 33113-2026 karta.png", "A 33113-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 52518-2022 karta.png", "A 52518-2022")</f>
         <v/>
       </c>
       <c r="Y75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 33113-2026 georefererad karta.tif", "A 33113-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 52518-2022 georefererad karta.tif", "A 52518-2022")</f>
         <v/>
       </c>
       <c r="AA75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 33113-2026 FSC-klagomål.docx", "A 33113-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 52518-2022 FSC-klagomål.docx", "A 52518-2022")</f>
         <v/>
       </c>
       <c r="AB75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 33113-2026 FSC-klagomål mail.docx", "A 33113-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 52518-2022 FSC-klagomål mail.docx", "A 52518-2022")</f>
         <v/>
       </c>
       <c r="AC75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 33113-2026 tillsynsbegäran.docx", "A 33113-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 52518-2022 tillsynsbegäran.docx", "A 52518-2022")</f>
         <v/>
       </c>
       <c r="AD75">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 33113-2026 tillsynsbegäran mail.docx", "A 33113-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 52518-2022 tillsynsbegäran mail.docx", "A 52518-2022")</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5230-2023</t>
+          <t>A 33113-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8899,10 +8905,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44959</v>
+        <v>46245</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8915,10 +8921,10 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -8927,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -8939,10 +8945,10 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8951,46 +8957,46 @@
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 5230-2023 artfynd.xlsx", "A 5230-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 33113-2026 artfynd.xlsx", "A 33113-2026")</f>
         <v/>
       </c>
       <c r="X76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 5230-2023 karta.png", "A 5230-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 33113-2026 karta.png", "A 33113-2026")</f>
         <v/>
       </c>
       <c r="Y76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 5230-2023 georefererad karta.tif", "A 5230-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 33113-2026 georefererad karta.tif", "A 33113-2026")</f>
         <v/>
       </c>
       <c r="AA76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 5230-2023 FSC-klagomål.docx", "A 5230-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 33113-2026 FSC-klagomål.docx", "A 33113-2026")</f>
         <v/>
       </c>
       <c r="AB76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 5230-2023 FSC-klagomål mail.docx", "A 5230-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 33113-2026 FSC-klagomål mail.docx", "A 33113-2026")</f>
         <v/>
       </c>
       <c r="AC76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 5230-2023 tillsynsbegäran.docx", "A 5230-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 33113-2026 tillsynsbegäran.docx", "A 33113-2026")</f>
         <v/>
       </c>
       <c r="AD76">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 5230-2023 tillsynsbegäran mail.docx", "A 5230-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 33113-2026 tillsynsbegäran mail.docx", "A 33113-2026")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1121-2026</t>
+          <t>A 5230-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9004,10 +9010,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46030</v>
+        <v>44959</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9020,7 +9026,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -9029,10 +9035,10 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
         <v>1</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
@@ -9047,7 +9053,7 @@
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -9056,46 +9062,46 @@
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 1121-2026 artfynd.xlsx", "A 1121-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 5230-2023 artfynd.xlsx", "A 5230-2023")</f>
         <v/>
       </c>
       <c r="X77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 1121-2026 karta.png", "A 1121-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 5230-2023 karta.png", "A 5230-2023")</f>
         <v/>
       </c>
       <c r="Y77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 1121-2026 georefererad karta.tif", "A 1121-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 5230-2023 georefererad karta.tif", "A 5230-2023")</f>
         <v/>
       </c>
       <c r="AA77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 1121-2026 FSC-klagomål.docx", "A 1121-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 5230-2023 FSC-klagomål.docx", "A 5230-2023")</f>
         <v/>
       </c>
       <c r="AB77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 1121-2026 FSC-klagomål mail.docx", "A 1121-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 5230-2023 FSC-klagomål mail.docx", "A 5230-2023")</f>
         <v/>
       </c>
       <c r="AC77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 1121-2026 tillsynsbegäran.docx", "A 1121-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 5230-2023 tillsynsbegäran.docx", "A 5230-2023")</f>
         <v/>
       </c>
       <c r="AD77">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 1121-2026 tillsynsbegäran mail.docx", "A 1121-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 5230-2023 tillsynsbegäran mail.docx", "A 5230-2023")</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29127-2024</t>
+          <t>A 1121-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9109,10 +9115,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45481</v>
+        <v>46030</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9125,17 +9131,17 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
         <v>1</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
@@ -9149,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -9161,46 +9167,46 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 29127-2024 artfynd.xlsx", "A 29127-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 1121-2026 artfynd.xlsx", "A 1121-2026")</f>
         <v/>
       </c>
       <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 29127-2024 karta.png", "A 29127-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 1121-2026 karta.png", "A 1121-2026")</f>
         <v/>
       </c>
       <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 29127-2024 georefererad karta.tif", "A 29127-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 1121-2026 georefererad karta.tif", "A 1121-2026")</f>
         <v/>
       </c>
       <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 29127-2024 FSC-klagomål.docx", "A 29127-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 1121-2026 FSC-klagomål.docx", "A 1121-2026")</f>
         <v/>
       </c>
       <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 29127-2024 FSC-klagomål mail.docx", "A 29127-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 1121-2026 FSC-klagomål mail.docx", "A 1121-2026")</f>
         <v/>
       </c>
       <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 29127-2024 tillsynsbegäran.docx", "A 29127-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 1121-2026 tillsynsbegäran.docx", "A 1121-2026")</f>
         <v/>
       </c>
       <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 29127-2024 tillsynsbegäran mail.docx", "A 29127-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 1121-2026 tillsynsbegäran mail.docx", "A 1121-2026")</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60357-2023</t>
+          <t>A 29127-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9210,14 +9216,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45258</v>
+        <v>45481</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9230,13 +9236,13 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J79" t="n">
         <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -9266,46 +9272,46 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 60357-2023 artfynd.xlsx", "A 60357-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 29127-2024 artfynd.xlsx", "A 29127-2024")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 60357-2023 karta.png", "A 60357-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 29127-2024 karta.png", "A 29127-2024")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 60357-2023 georefererad karta.tif", "A 60357-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 29127-2024 georefererad karta.tif", "A 29127-2024")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 60357-2023 FSC-klagomål.docx", "A 60357-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 29127-2024 FSC-klagomål.docx", "A 29127-2024")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 60357-2023 FSC-klagomål mail.docx", "A 60357-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 29127-2024 FSC-klagomål mail.docx", "A 29127-2024")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 60357-2023 tillsynsbegäran.docx", "A 60357-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 29127-2024 tillsynsbegäran.docx", "A 29127-2024")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 60357-2023 tillsynsbegäran mail.docx", "A 60357-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 29127-2024 tillsynsbegäran mail.docx", "A 29127-2024")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7069-2024</t>
+          <t>A 60357-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9315,14 +9321,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45343</v>
+        <v>45258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9335,13 +9341,13 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>9.1</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -9375,42 +9381,42 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="W80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 7069-2024 artfynd.xlsx", "A 7069-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 60357-2023 artfynd.xlsx", "A 60357-2023")</f>
         <v/>
       </c>
       <c r="X80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 7069-2024 karta.png", "A 7069-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 60357-2023 karta.png", "A 60357-2023")</f>
         <v/>
       </c>
       <c r="Y80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 7069-2024 georefererad karta.tif", "A 7069-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 60357-2023 georefererad karta.tif", "A 60357-2023")</f>
         <v/>
       </c>
       <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 7069-2024 FSC-klagomål.docx", "A 7069-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 60357-2023 FSC-klagomål.docx", "A 60357-2023")</f>
         <v/>
       </c>
       <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 7069-2024 FSC-klagomål mail.docx", "A 7069-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 60357-2023 FSC-klagomål mail.docx", "A 60357-2023")</f>
         <v/>
       </c>
       <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 7069-2024 tillsynsbegäran.docx", "A 7069-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 60357-2023 tillsynsbegäran.docx", "A 60357-2023")</f>
         <v/>
       </c>
       <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 7069-2024 tillsynsbegäran mail.docx", "A 7069-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 60357-2023 tillsynsbegäran mail.docx", "A 60357-2023")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59920-2023</t>
+          <t>A 7069-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9420,14 +9426,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45257</v>
+        <v>45343</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9440,16 +9446,16 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -9464,7 +9470,7 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -9480,42 +9486,42 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Öring</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 59920-2023 artfynd.xlsx", "A 59920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 7069-2024 artfynd.xlsx", "A 7069-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 59920-2023 karta.png", "A 59920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 7069-2024 karta.png", "A 7069-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 59920-2023 georefererad karta.tif", "A 59920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 7069-2024 georefererad karta.tif", "A 7069-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 59920-2023 FSC-klagomål.docx", "A 59920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 7069-2024 FSC-klagomål.docx", "A 7069-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 59920-2023 FSC-klagomål mail.docx", "A 59920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 7069-2024 FSC-klagomål mail.docx", "A 7069-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 59920-2023 tillsynsbegäran.docx", "A 59920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 7069-2024 tillsynsbegäran.docx", "A 7069-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 59920-2023 tillsynsbegäran mail.docx", "A 59920-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 7069-2024 tillsynsbegäran mail.docx", "A 7069-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13425-2022</t>
+          <t>A 59920-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9525,14 +9531,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44645</v>
+        <v>45257</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9545,19 +9551,19 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>16.8</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
         <v>1</v>
       </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -9572,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9585,59 +9591,59 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 13425-2022 artfynd.xlsx", "A 13425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 59920-2023 artfynd.xlsx", "A 59920-2023")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 13425-2022 karta.png", "A 13425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 59920-2023 karta.png", "A 59920-2023")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 13425-2022 georefererad karta.tif", "A 13425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 59920-2023 georefererad karta.tif", "A 59920-2023")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 13425-2022 FSC-klagomål.docx", "A 13425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 59920-2023 FSC-klagomål.docx", "A 59920-2023")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 13425-2022 FSC-klagomål mail.docx", "A 13425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 59920-2023 FSC-klagomål mail.docx", "A 59920-2023")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 13425-2022 tillsynsbegäran.docx", "A 13425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 59920-2023 tillsynsbegäran.docx", "A 59920-2023")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 13425-2022 tillsynsbegäran mail.docx", "A 13425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 59920-2023 tillsynsbegäran mail.docx", "A 59920-2023")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S 1509-2022</t>
+          <t>A 13425-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44638</v>
+        <v>44645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9650,7 +9656,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>16.8</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -9690,39 +9696,35 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/S 1509-2022 artfynd.xlsx", "S 1509-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/artfynd/A 13425-2022 artfynd.xlsx", "A 13425-2022")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/S 1509-2022 karta.png", "S 1509-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor/A 13425-2022 karta.png", "A 13425-2022")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/S 1509-2022 georefererad karta.tif", "S 1509-2022")</f>
-        <v/>
-      </c>
-      <c r="Z83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/knärot/S 1509-2022 karta knärot.png", "S 1509-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/kartor_geotiff/A 13425-2022 georefererad karta.tif", "A 13425-2022")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/S 1509-2022 FSC-klagomål.docx", "S 1509-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomål/A 13425-2022 FSC-klagomål.docx", "A 13425-2022")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/S 1509-2022 FSC-klagomål mail.docx", "S 1509-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/klagomålsmail/A 13425-2022 FSC-klagomål mail.docx", "A 13425-2022")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/S 1509-2022 tillsynsbegäran.docx", "S 1509-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsyn/A 13425-2022 tillsynsbegäran.docx", "A 13425-2022")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/S 1509-2022 tillsynsbegäran mail.docx", "S 1509-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1882/tillsynsmail/A 13425-2022 tillsynsbegäran mail.docx", "A 13425-2022")</f>
         <v/>
       </c>
     </row>
@@ -9746,7 +9748,7 @@
         <v>45627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9851,7 +9853,7 @@
         <v>44495</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9924,7 +9926,7 @@
         <v>44530</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9997,7 +9999,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10070,7 +10072,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10143,7 +10145,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10216,7 +10218,7 @@
         <v>44606</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10294,7 +10296,7 @@
         <v>44889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10367,7 +10369,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10440,7 +10442,7 @@
         <v>44509</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10513,7 +10515,7 @@
         <v>44783</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10586,7 +10588,7 @@
         <v>44733</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10659,7 +10661,7 @@
         <v>44825</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10732,7 +10734,7 @@
         <v>44516</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10810,7 +10812,7 @@
         <v>44844</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10883,7 +10885,7 @@
         <v>44607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10956,7 +10958,7 @@
         <v>44818</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11034,7 +11036,7 @@
         <v>44647</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11112,7 +11114,7 @@
         <v>44510</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11185,7 +11187,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11258,7 +11260,7 @@
         <v>44753</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11336,7 +11338,7 @@
         <v>44866</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11409,7 +11411,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11482,7 +11484,7 @@
         <v>44528</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11555,7 +11557,7 @@
         <v>44522</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11628,7 +11630,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11701,7 +11703,7 @@
         <v>44781</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11774,7 +11776,7 @@
         <v>44510</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11847,7 +11849,7 @@
         <v>44767</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11920,7 +11922,7 @@
         <v>44764</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11993,7 +11995,7 @@
         <v>44756</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12066,7 +12068,7 @@
         <v>44610</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12139,7 +12141,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12217,7 +12219,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12295,7 +12297,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12368,7 +12370,7 @@
         <v>44512</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12446,7 +12448,7 @@
         <v>44530</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12524,7 +12526,7 @@
         <v>44637</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12597,7 +12599,7 @@
         <v>44733</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12670,7 +12672,7 @@
         <v>44850</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12743,7 +12745,7 @@
         <v>44629</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12816,7 +12818,7 @@
         <v>44637</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12889,7 +12891,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12962,7 +12964,7 @@
         <v>44638</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13035,7 +13037,7 @@
         <v>44714</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13108,7 +13110,7 @@
         <v>44509</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13186,7 +13188,7 @@
         <v>44637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13259,7 +13261,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13332,7 +13334,7 @@
         <v>44486</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13405,7 +13407,7 @@
         <v>44796</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13478,7 +13480,7 @@
         <v>44514</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13551,7 +13553,7 @@
         <v>44641</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13629,7 +13631,7 @@
         <v>44523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13702,7 +13704,7 @@
         <v>44592</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13775,7 +13777,7 @@
         <v>44650</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13848,7 +13850,7 @@
         <v>44497</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13921,7 +13923,7 @@
         <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13994,7 +13996,7 @@
         <v>44945</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14067,7 +14069,7 @@
         <v>44687</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14145,7 +14147,7 @@
         <v>45348</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14218,7 +14220,7 @@
         <v>45373</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14291,7 +14293,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14364,7 +14366,7 @@
         <v>44608</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14437,7 +14439,7 @@
         <v>44608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14510,7 +14512,7 @@
         <v>45224</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14583,7 +14585,7 @@
         <v>45078</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14656,7 +14658,7 @@
         <v>45162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14729,7 +14731,7 @@
         <v>44859</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14802,7 +14804,7 @@
         <v>45517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14875,7 +14877,7 @@
         <v>45307</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14948,7 +14950,7 @@
         <v>45741</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15021,7 +15023,7 @@
         <v>45035</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15094,7 +15096,7 @@
         <v>45715</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15167,7 +15169,7 @@
         <v>44497</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15240,7 +15242,7 @@
         <v>44631</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15313,7 +15315,7 @@
         <v>45343</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15386,7 +15388,7 @@
         <v>45656</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15459,7 +15461,7 @@
         <v>45453</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15532,7 +15534,7 @@
         <v>45453</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15605,7 +15607,7 @@
         <v>44864</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15678,7 +15680,7 @@
         <v>45254</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15751,7 +15753,7 @@
         <v>44950</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15824,7 +15826,7 @@
         <v>45208</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15902,7 +15904,7 @@
         <v>44734</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15975,7 +15977,7 @@
         <v>45115</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16053,7 +16055,7 @@
         <v>45115</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16131,7 +16133,7 @@
         <v>45453</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16209,7 +16211,7 @@
         <v>45510</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16282,7 +16284,7 @@
         <v>44487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16355,7 +16357,7 @@
         <v>44866</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16428,7 +16430,7 @@
         <v>45072</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16501,7 +16503,7 @@
         <v>44967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16574,7 +16576,7 @@
         <v>45572</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16652,7 +16654,7 @@
         <v>45104</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16725,7 +16727,7 @@
         <v>44568</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16803,7 +16805,7 @@
         <v>45158</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16881,7 +16883,7 @@
         <v>44928</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16954,7 +16956,7 @@
         <v>45027</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17027,7 +17029,7 @@
         <v>45170</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17105,7 +17107,7 @@
         <v>44809</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17178,7 +17180,7 @@
         <v>45000</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17251,7 +17253,7 @@
         <v>44593</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17329,7 +17331,7 @@
         <v>44558</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17402,7 +17404,7 @@
         <v>45708</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17475,7 +17477,7 @@
         <v>45198</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17548,7 +17550,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17626,7 +17628,7 @@
         <v>45484</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17699,7 +17701,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17772,7 +17774,7 @@
         <v>44865</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17845,7 +17847,7 @@
         <v>45502</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17918,7 +17920,7 @@
         <v>45471</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17996,7 +17998,7 @@
         <v>44828</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18069,7 +18071,7 @@
         <v>45817</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18142,7 +18144,7 @@
         <v>46030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18215,7 +18217,7 @@
         <v>44959</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18288,7 +18290,7 @@
         <v>45975</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18361,7 +18363,7 @@
         <v>45964</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18439,7 +18441,7 @@
         <v>45238</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18512,7 +18514,7 @@
         <v>45834</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18585,7 +18587,7 @@
         <v>45072</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18658,7 +18660,7 @@
         <v>45817</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18731,7 +18733,7 @@
         <v>44503</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18804,7 +18806,7 @@
         <v>45897</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18877,7 +18879,7 @@
         <v>45211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18950,7 +18952,7 @@
         <v>45105</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19023,7 +19025,7 @@
         <v>45937</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19101,7 +19103,7 @@
         <v>45933</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19179,7 +19181,7 @@
         <v>45904</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19252,7 +19254,7 @@
         <v>45439</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19325,7 +19327,7 @@
         <v>45103</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19398,7 +19400,7 @@
         <v>44610</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19471,7 +19473,7 @@
         <v>45903</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19544,7 +19546,7 @@
         <v>45707</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19622,7 +19624,7 @@
         <v>45364</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19695,7 +19697,7 @@
         <v>44606</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19768,7 +19770,7 @@
         <v>45322</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19841,7 +19843,7 @@
         <v>45599</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19914,7 +19916,7 @@
         <v>46142</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19992,7 +19994,7 @@
         <v>46142</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20070,7 +20072,7 @@
         <v>46142</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20148,7 +20150,7 @@
         <v>46142</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20226,7 +20228,7 @@
         <v>45917</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20299,7 +20301,7 @@
         <v>44511</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20372,7 +20374,7 @@
         <v>45607</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20450,7 +20452,7 @@
         <v>45922</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20523,7 +20525,7 @@
         <v>45930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20596,7 +20598,7 @@
         <v>44734</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20669,7 +20671,7 @@
         <v>45936</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20742,7 +20744,7 @@
         <v>45434</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20820,7 +20822,7 @@
         <v>44573</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20893,7 +20895,7 @@
         <v>45253</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20966,7 +20968,7 @@
         <v>44804</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21039,7 +21041,7 @@
         <v>45162</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21112,7 +21114,7 @@
         <v>45790</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21185,7 +21187,7 @@
         <v>45469</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21258,7 +21260,7 @@
         <v>45105</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21331,7 +21333,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21409,7 +21411,7 @@
         <v>45254</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21482,7 +21484,7 @@
         <v>45964</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21560,7 +21562,7 @@
         <v>45107</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21633,7 +21635,7 @@
         <v>45303</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21706,7 +21708,7 @@
         <v>46154</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21784,7 +21786,7 @@
         <v>45608</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21862,7 +21864,7 @@
         <v>46157</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21935,7 +21937,7 @@
         <v>44970</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22008,7 +22010,7 @@
         <v>45958</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22086,7 +22088,7 @@
         <v>45964</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22164,7 +22166,7 @@
         <v>45599</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22237,7 +22239,7 @@
         <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22315,7 +22317,7 @@
         <v>45587</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22393,7 +22395,7 @@
         <v>45391</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22466,7 +22468,7 @@
         <v>45964</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22544,7 +22546,7 @@
         <v>45964</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22622,7 +22624,7 @@
         <v>45303</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22695,7 +22697,7 @@
         <v>44573</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22768,7 +22770,7 @@
         <v>46163</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22846,7 +22848,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22919,7 +22921,7 @@
         <v>46163</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22997,7 +22999,7 @@
         <v>46153</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23070,7 +23072,7 @@
         <v>45327</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23143,7 +23145,7 @@
         <v>46163</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23221,7 +23223,7 @@
         <v>46163</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23299,7 +23301,7 @@
         <v>45525</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23377,7 +23379,7 @@
         <v>44697</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23450,7 +23452,7 @@
         <v>45986</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23523,7 +23525,7 @@
         <v>45441</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23596,7 +23598,7 @@
         <v>45987</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23669,7 +23671,7 @@
         <v>45246</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23742,7 +23744,7 @@
         <v>46007</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23815,7 +23817,7 @@
         <v>44662</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23888,7 +23890,7 @@
         <v>45994</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23961,7 +23963,7 @@
         <v>46001</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24034,7 +24036,7 @@
         <v>46058</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24107,7 +24109,7 @@
         <v>45427</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24185,7 +24187,7 @@
         <v>46170</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24258,7 +24260,7 @@
         <v>44808</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24331,7 +24333,7 @@
         <v>46170</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24404,7 +24406,7 @@
         <v>45198</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24477,7 +24479,7 @@
         <v>44995</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24555,7 +24557,7 @@
         <v>46174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24633,7 +24635,7 @@
         <v>46174</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24711,7 +24713,7 @@
         <v>46010</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24784,7 +24786,7 @@
         <v>45455</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24857,7 +24859,7 @@
         <v>46010</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24930,7 +24932,7 @@
         <v>45373</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25003,7 +25005,7 @@
         <v>46174</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25081,7 +25083,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25159,7 +25161,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25237,7 +25239,7 @@
         <v>45404</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25315,7 +25317,7 @@
         <v>44676</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25388,7 +25390,7 @@
         <v>44909</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25461,7 +25463,7 @@
         <v>44753</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25539,7 +25541,7 @@
         <v>46171</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25612,7 +25614,7 @@
         <v>46030</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25685,7 +25687,7 @@
         <v>46030</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25758,7 +25760,7 @@
         <v>46030</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25831,7 +25833,7 @@
         <v>44999</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25904,7 +25906,7 @@
         <v>44999</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25977,7 +25979,7 @@
         <v>45022</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26050,7 +26052,7 @@
         <v>45609</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26123,7 +26125,7 @@
         <v>45533</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26201,7 +26203,7 @@
         <v>46030</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26274,7 +26276,7 @@
         <v>45408</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26352,7 +26354,7 @@
         <v>46043</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26425,7 +26427,7 @@
         <v>46042</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26498,7 +26500,7 @@
         <v>46042</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26571,7 +26573,7 @@
         <v>46042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26644,7 +26646,7 @@
         <v>46045</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26722,7 +26724,7 @@
         <v>44957</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26795,7 +26797,7 @@
         <v>46181</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26868,7 +26870,7 @@
         <v>45188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26946,7 +26948,7 @@
         <v>46181</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27019,7 +27021,7 @@
         <v>45456</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27092,7 +27094,7 @@
         <v>44494</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27165,7 +27167,7 @@
         <v>46181</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27238,7 +27240,7 @@
         <v>46182</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27311,7 +27313,7 @@
         <v>46176</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27384,7 +27386,7 @@
         <v>44999</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27457,7 +27459,7 @@
         <v>45301</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27530,7 +27532,7 @@
         <v>44578</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27603,7 +27605,7 @@
         <v>46184</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27676,7 +27678,7 @@
         <v>46184</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27749,7 +27751,7 @@
         <v>46184</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27822,7 +27824,7 @@
         <v>46185</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27900,7 +27902,7 @@
         <v>46069</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27973,7 +27975,7 @@
         <v>46069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28046,7 +28048,7 @@
         <v>46071</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28119,7 +28121,7 @@
         <v>45115</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28197,7 +28199,7 @@
         <v>46181</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28270,7 +28272,7 @@
         <v>44889</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28343,7 +28345,7 @@
         <v>45226</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28416,7 +28418,7 @@
         <v>45664</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28489,7 +28491,7 @@
         <v>45664</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28562,7 +28564,7 @@
         <v>46185</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28640,7 +28642,7 @@
         <v>46185</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28718,7 +28720,7 @@
         <v>46080</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28791,7 +28793,7 @@
         <v>45162</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28864,7 +28866,7 @@
         <v>46189</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28937,7 +28939,7 @@
         <v>46189</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29010,7 +29012,7 @@
         <v>46189</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29083,7 +29085,7 @@
         <v>44748</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29156,7 +29158,7 @@
         <v>44915</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29229,7 +29231,7 @@
         <v>46095</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29302,7 +29304,7 @@
         <v>46196</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29375,7 +29377,7 @@
         <v>46196</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29448,7 +29450,7 @@
         <v>45510</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29521,7 +29523,7 @@
         <v>45473</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29594,7 +29596,7 @@
         <v>46196</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29667,7 +29669,7 @@
         <v>46198</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29740,7 +29742,7 @@
         <v>44739</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29813,7 +29815,7 @@
         <v>46198</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29886,7 +29888,7 @@
         <v>46198</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29959,7 +29961,7 @@
         <v>46112</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30037,7 +30039,7 @@
         <v>46112</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30115,7 +30117,7 @@
         <v>46112</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30193,7 +30195,7 @@
         <v>45042</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30266,7 +30268,7 @@
         <v>45525</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30339,7 +30341,7 @@
         <v>45285</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30412,7 +30414,7 @@
         <v>46184</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30485,7 +30487,7 @@
         <v>46120</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30558,7 +30560,7 @@
         <v>45481</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30631,7 +30633,7 @@
         <v>45217</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30704,7 +30706,7 @@
         <v>44606</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30777,7 +30779,7 @@
         <v>45385</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30855,7 +30857,7 @@
         <v>46127</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30933,7 +30935,7 @@
         <v>45132</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31006,7 +31008,7 @@
         <v>44595</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31079,7 +31081,7 @@
         <v>45104</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31152,7 +31154,7 @@
         <v>45104</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31225,7 +31227,7 @@
         <v>45827</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31303,7 +31305,7 @@
         <v>45714</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31376,7 +31378,7 @@
         <v>45030</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31449,7 +31451,7 @@
         <v>44487</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31522,7 +31524,7 @@
         <v>45572</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31595,7 +31597,7 @@
         <v>44812</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31668,7 +31670,7 @@
         <v>44907</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31746,7 +31748,7 @@
         <v>45072</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31819,7 +31821,7 @@
         <v>45495</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31892,7 +31894,7 @@
         <v>45469</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31965,7 +31967,7 @@
         <v>45511</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32038,7 +32040,7 @@
         <v>46210</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32116,7 +32118,7 @@
         <v>46210</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32194,7 +32196,7 @@
         <v>46210</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32272,7 +32274,7 @@
         <v>46210</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32350,7 +32352,7 @@
         <v>45190</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32423,7 +32425,7 @@
         <v>45235</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32501,7 +32503,7 @@
         <v>46216</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32579,7 +32581,7 @@
         <v>46216</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32657,7 +32659,7 @@
         <v>45391</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32730,7 +32732,7 @@
         <v>44615</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32803,7 +32805,7 @@
         <v>44602</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32876,7 +32878,7 @@
         <v>45719</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32949,7 +32951,7 @@
         <v>44791</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33022,7 +33024,7 @@
         <v>46230</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33095,7 +33097,7 @@
         <v>45448</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33173,7 +33175,7 @@
         <v>46230</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33246,7 +33248,7 @@
         <v>46230</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33319,7 +33321,7 @@
         <v>46230</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33392,7 +33394,7 @@
         <v>45506</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33470,7 +33472,7 @@
         <v>45191</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33543,7 +33545,7 @@
         <v>46275</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33621,7 +33623,7 @@
         <v>46275</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33699,7 +33701,7 @@
         <v>44641</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33777,7 +33779,7 @@
         <v>44999</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33850,7 +33852,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33923,7 +33925,7 @@
         <v>46237</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33996,7 +33998,7 @@
         <v>44609</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34069,7 +34071,7 @@
         <v>46230</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34142,7 +34144,7 @@
         <v>46237</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34215,7 +34217,7 @@
         <v>44950</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34288,7 +34290,7 @@
         <v>44950</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34361,7 +34363,7 @@
         <v>45586</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34434,7 +34436,7 @@
         <v>46230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34507,7 +34509,7 @@
         <v>46283</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34580,7 +34582,7 @@
         <v>45267</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34653,7 +34655,7 @@
         <v>44488</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34726,7 +34728,7 @@
         <v>44552</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34799,7 +34801,7 @@
         <v>46287</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34872,7 +34874,7 @@
         <v>45511</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34945,7 +34947,7 @@
         <v>45327</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35018,7 +35020,7 @@
         <v>44844</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35091,7 +35093,7 @@
         <v>44995</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35169,7 +35171,7 @@
         <v>46289</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35247,7 +35249,7 @@
         <v>46289</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35325,7 +35327,7 @@
         <v>45184</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35403,7 +35405,7 @@
         <v>46290</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35481,7 +35483,7 @@
         <v>44487</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35554,7 +35556,7 @@
         <v>46290</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35632,7 +35634,7 @@
         <v>44733</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35710,7 +35712,7 @@
         <v>46290</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35788,7 +35790,7 @@
         <v>45481</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35866,7 +35868,7 @@
         <v>46290</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35944,7 +35946,7 @@
         <v>44501</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36017,7 +36019,7 @@
         <v>44517</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36090,7 +36092,7 @@
         <v>46290</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36168,7 +36170,7 @@
         <v>46290</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36246,7 +36248,7 @@
         <v>44642</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36319,7 +36321,7 @@
         <v>46252</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36392,7 +36394,7 @@
         <v>45007</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36465,7 +36467,7 @@
         <v>45254</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36538,7 +36540,7 @@
         <v>44497</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36611,7 +36613,7 @@
         <v>46252</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36684,7 +36686,7 @@
         <v>46252</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36757,7 +36759,7 @@
         <v>46253</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36830,7 +36832,7 @@
         <v>46297</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36908,7 +36910,7 @@
         <v>46297</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36986,7 +36988,7 @@
         <v>46297</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37064,7 +37066,7 @@
         <v>46297</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37142,7 +37144,7 @@
         <v>46297</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37220,7 +37222,7 @@
         <v>44641</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37298,7 +37300,7 @@
         <v>46297</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37376,7 +37378,7 @@
         <v>46297</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37454,7 +37456,7 @@
         <v>46254</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37527,7 +37529,7 @@
         <v>46297</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37605,7 +37607,7 @@
         <v>46297</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37683,7 +37685,7 @@
         <v>46297</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37761,7 +37763,7 @@
         <v>45664</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37834,7 +37836,7 @@
         <v>45777</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37907,7 +37909,7 @@
         <v>45601</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37980,7 +37982,7 @@
         <v>45559</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38053,7 +38055,7 @@
         <v>45303</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38126,7 +38128,7 @@
         <v>45470</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38199,7 +38201,7 @@
         <v>46258</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38272,7 +38274,7 @@
         <v>45407</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38345,7 +38347,7 @@
         <v>46303</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38418,7 +38420,7 @@
         <v>45667</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38491,7 +38493,7 @@
         <v>45617</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38564,7 +38566,7 @@
         <v>45569</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38637,7 +38639,7 @@
         <v>45303</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38710,7 +38712,7 @@
         <v>45720</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38783,7 +38785,7 @@
         <v>45680</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38861,7 +38863,7 @@
         <v>46309</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38939,7 +38941,7 @@
         <v>46309</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39017,7 +39019,7 @@
         <v>46268</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39095,7 +39097,7 @@
         <v>46268</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39168,7 +39170,7 @@
         <v>45825</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39241,7 +39243,7 @@
         <v>45485</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39314,7 +39316,7 @@
         <v>45485</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39392,7 +39394,7 @@
         <v>45485</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39465,7 +39467,7 @@
         <v>44498</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39538,7 +39540,7 @@
         <v>44662</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39611,7 +39613,7 @@
         <v>44648</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39684,7 +39686,7 @@
         <v>44739</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39757,7 +39759,7 @@
         <v>45733</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39830,7 +39832,7 @@
         <v>45642</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39903,7 +39905,7 @@
         <v>44855</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39976,7 +39978,7 @@
         <v>45835</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40049,7 +40051,7 @@
         <v>45257</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40122,7 +40124,7 @@
         <v>45572</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40200,7 +40202,7 @@
         <v>45742</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40273,7 +40275,7 @@
         <v>43993</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40346,7 +40348,7 @@
         <v>44655</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40424,7 +40426,7 @@
         <v>46219</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40497,7 +40499,7 @@
         <v>46286</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40575,7 +40577,7 @@
         <v>46288</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40653,7 +40655,7 @@
         <v>46268</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40731,7 +40733,7 @@
         <v>46267</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44587</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45635</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44574</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44579</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44757</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44929</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46268</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45349</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45656</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>45228</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>45674</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>44950</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45362</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>45212</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>44993</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45525</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>45810</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45111</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>46290</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45681</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45824</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>44973</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>44714</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>45680</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>46174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>44722</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>46281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>46259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>44518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44595</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45244</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45575</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44859</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45030</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45674</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44942</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45313</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>45629</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>45104</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45575</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44508</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44859</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>46085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45447</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>46275</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45708</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>46245</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44959</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46030</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>45481</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>45258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45343</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45257</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44495</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44530</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44606</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44509</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44783</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44733</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44825</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44516</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44844</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44607</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>44818</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44647</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44510</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44753</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>44866</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>44528</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>44522</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44781</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44510</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44767</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44764</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44756</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44610</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44512</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44530</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44637</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44733</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44850</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44629</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>44637</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>44638</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44714</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44509</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44486</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44796</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44514</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44641</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44592</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44650</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44497</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44945</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44687</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45348</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45373</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>44608</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45224</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>45078</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44859</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45307</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45741</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45035</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45715</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>44497</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44631</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45343</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45656</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>45453</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45453</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44864</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45254</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>44950</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45208</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44734</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45115</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45115</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45453</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>45510</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>44487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44866</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45072</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>44967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45572</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45104</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>44568</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45158</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>44928</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45027</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45170</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44809</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>45000</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44593</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44558</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45708</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45198</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45484</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44865</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45502</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45471</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44828</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45817</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>46030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>44959</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45975</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45964</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45238</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45834</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>45072</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45817</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44503</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>45897</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45105</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45937</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45933</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45904</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45439</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45103</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44610</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45903</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45707</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45364</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>44606</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45322</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>45599</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>46142</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>46142</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>46142</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>46142</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45917</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>44511</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45607</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>45922</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44734</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45936</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45434</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>44573</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>45253</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44804</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45162</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45790</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45469</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45105</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45254</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45964</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45107</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45303</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>46154</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45608</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>46157</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44970</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45958</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45964</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45599</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44655</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45587</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45391</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45964</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45964</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45303</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44573</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>46163</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>46163</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>46153</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45327</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>46163</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46163</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45525</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>44697</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45986</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>45441</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45987</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45246</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>46007</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44662</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45994</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46001</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>46058</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45427</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>46170</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>44808</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>46170</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45198</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>44995</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>46174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46174</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>46010</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45455</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46010</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45373</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>46174</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45404</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44676</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44909</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>44753</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46171</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>46030</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>46030</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46030</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44999</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44999</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45022</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45609</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>45533</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>46030</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45408</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>46043</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>46042</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>46042</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>46042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>46045</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>44957</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>46181</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>46181</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>45456</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>44494</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>46181</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46182</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>46176</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44999</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45301</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44578</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46184</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46184</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46184</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46185</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>46069</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>46071</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45115</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46181</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44889</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45226</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45664</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45664</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>46185</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>46185</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28720,7 +28720,7 @@
         <v>46080</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45162</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>46189</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46189</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>46189</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>44748</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44915</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>46095</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>46196</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>46196</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>45510</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45473</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>46196</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>46198</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44739</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>46198</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>46198</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>46112</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>46112</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>46112</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45042</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>45525</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45285</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>46184</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46120</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45481</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45217</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>44606</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45385</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46127</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45132</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>44595</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45104</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45104</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45827</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45714</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45030</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>44487</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45572</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>44812</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44907</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45072</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45495</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>45469</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45511</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>46210</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>46210</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>46210</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46210</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45190</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45235</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>46216</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>46216</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45391</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>44615</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44602</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45719</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44791</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>46230</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45448</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>46230</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>46230</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>46230</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45506</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45191</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>46275</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>46275</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>44641</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44999</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>46237</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>44609</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>46230</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>46237</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>44950</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>44950</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45586</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>46230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>46283</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>45267</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>44488</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>44552</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>46287</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45511</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45327</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>44844</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>44995</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46289</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>46289</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45184</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>46290</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>44487</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>46290</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>44733</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>46290</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45481</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>46290</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>44501</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>44517</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>46290</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>46290</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>44642</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>46252</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45007</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45254</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44497</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>46252</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>46252</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>46253</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>46297</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46297</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>46297</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>46297</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>46297</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44641</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>46297</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37378,7 +37378,7 @@
         <v>46297</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>46254</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>46297</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>46297</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>46297</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45664</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45777</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45601</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45559</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45303</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45470</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>46258</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45407</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>46303</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45667</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>45617</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45569</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45303</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45720</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45680</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>46309</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>46309</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>46268</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>46268</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45825</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45485</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45485</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45485</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44498</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>44662</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44648</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>44739</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45733</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45642</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44855</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45835</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>45257</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45572</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>45742</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>43993</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>44655</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>46219</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>46286</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>46288</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46268</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>46267</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>46311</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44587</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45629</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>45635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44950</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>44579</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>46281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46126</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>46268</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>46280</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45107</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45674</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>44950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>45349</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>44587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>45228</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>45656</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45362</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44518</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45810</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45681</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>45824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>46314</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>45575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>44993</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45525</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45111</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>44812</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45212</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44638</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44973</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>44714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>46174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>46259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45680</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44508</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45674</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45244</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45510</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45481</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45104</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44508</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45575</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44942</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45258</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45343</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>46245</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>46030</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44645</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45257</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>46085</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44874</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44859</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44959</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44676</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>46275</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45447</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>45629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45546</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45313</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44593</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45575</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44859</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45708</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45627</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44495</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>44518</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>44530</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>44606</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>44889</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44509</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44783</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44844</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44607</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44647</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44510</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44753</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44866</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44528</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>44522</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44781</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44510</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>44767</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44764</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44756</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44610</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>44530</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44512</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44637</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44733</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44850</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44629</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44637</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>44638</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44831</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44714</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44509</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44796</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44514</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44641</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44523</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44592</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44650</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44928</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44497</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44497</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44859</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44733</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45817</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45246</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45343</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45042</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45817</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45170</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45184</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45572</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44791</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45897</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45211</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45208</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44739</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45238</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44864</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45254</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45903</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>46157</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46153</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44511</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45599</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44970</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46163</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45599</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44606</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44945</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>46163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>46163</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44995</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>46163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>45922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>46058</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>46007</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44655</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>46171</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>46170</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>46174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45936</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45373</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44844</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45502</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>46174</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>46174</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>46174</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>45373</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>45391</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>45453</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44809</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45439</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45105</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45455</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45469</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>44497</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>44957</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>46181</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>46181</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>46181</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>46176</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45162</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>46184</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45495</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>46184</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>46184</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>46182</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45958</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>46185</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>46185</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44631</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>46181</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45224</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45481</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>45964</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>46189</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>46189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45964</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>46189</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45089</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45964</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44501</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45104</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45664</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45664</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45434</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45715</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45664</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46198</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>46196</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>46196</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46184</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>46198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45708</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45533</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45484</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>45987</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45473</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>46210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46210</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>46210</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45253</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46210</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44950</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44950</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>46216</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>46216</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>44999</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46001</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>45777</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45303</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45559</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>46230</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45601</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46230</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>46230</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45470</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46237</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46237</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45667</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45407</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>46010</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>46281</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45569</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>46030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>46030</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>46030</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>46283</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45617</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45720</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>46287</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>46042</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>46042</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46030</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45680</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>46043</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45303</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>46045</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>46289</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46290</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>46290</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>46290</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>46290</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>46290</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>46290</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>46289</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>46069</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>46069</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44517</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>46071</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45825</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>44498</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45642</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>44648</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45485</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45485</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>44662</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44855</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>44739</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45733</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>45485</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>46253</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>46252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46080</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>46252</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>46252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46297</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>46297</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>45835</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>46297</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>46297</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>46095</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>46297</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>46254</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>46297</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>46297</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>46297</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>46297</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>46297</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45235</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45427</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45586</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45742</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45572</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45257</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45481</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>46112</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46258</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46112</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>46112</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>46303</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46120</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>46127</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44999</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>44999</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>44915</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>44642</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>45827</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>44552</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46309</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>44995</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>46309</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45904</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>44959</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45348</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45072</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45937</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46268</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44812</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45364</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46314</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46230</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45975</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46230</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>44615</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45132</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45322</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>46314</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45103</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45834</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>46030</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44950</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45510</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>44568</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>45933</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44676</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45030</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45408</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45587</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45714</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45707</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45385</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>46142</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>46275</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45404</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46275</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>46142</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46142</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46142</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44734</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45964</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44641</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>46154</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45896</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45790</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45303</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45115</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45027</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45226</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45267</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44609</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44828</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45506</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45022</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44999</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45607</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45158</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>45656</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>44753</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44748</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45719</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45517</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>45511</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>44573</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45072</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45741</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44595</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45105</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>45510</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>44859</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45391</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45115</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45115</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44608</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44503</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44907</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45254</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45609</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45525</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44558</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45078</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45000</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45608</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44494</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45303</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45511</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45572</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>44866</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45190</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>44608</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44608</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44967</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45327</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>45162</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44578</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>45104</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>44602</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>44662</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45198</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>44697</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>44606</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44641</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45217</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45072</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45191</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45162</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>45198</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45456</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44808</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45254</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45208</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44804</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45188</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45307</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45285</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44734</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45448</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>44687</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45471</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45007</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45301</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45441</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>44889</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45327</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45107</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>44865</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>45453</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45453</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45525</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>44573</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>44610</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>44909</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>43993</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>44655</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>46219</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>46286</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>46288</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>46268</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>

--- a/Översikt ASKERSUND.xlsx
+++ b/Översikt ASKERSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>44620</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>46070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>45610</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>46311</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44587</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45629</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>45635</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44950</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>44574</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>44579</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>44757</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>46281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46126</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>44929</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>46268</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>46280</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45107</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45674</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>44950</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>45349</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>44587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>45228</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>45656</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45362</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>44518</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45810</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>45681</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>45824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>46314</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>45575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>44993</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45525</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45111</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>44812</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45212</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44638</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>44973</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>44714</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>46174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>46259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45680</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44508</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45674</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45244</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45510</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45481</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45104</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44508</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45575</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44942</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45258</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45343</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>46245</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>46030</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44645</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45257</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>46085</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44874</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44859</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44959</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44676</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>46275</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45447</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>45629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45546</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45313</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>44593</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45575</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44859</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45708</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45627</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44495</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>44518</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>44530</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>44606</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>44889</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44509</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44783</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44516</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44844</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44607</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44647</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44510</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44753</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44866</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44528</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>44522</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44781</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44510</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>44767</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44764</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44756</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44610</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>44530</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44512</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44637</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44733</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44850</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44629</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44637</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>44638</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44831</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44714</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44509</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44796</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44514</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44641</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44523</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44592</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44650</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44928</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44497</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44497</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44859</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44733</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45817</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45246</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45343</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45042</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45817</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45170</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45184</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45572</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44791</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45897</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45211</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45208</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44739</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45238</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44864</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45254</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45903</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>46157</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46153</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44511</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45599</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44970</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46163</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45599</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>44606</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44945</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>46163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>46163</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44995</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>46163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>45922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>46058</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>46007</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44655</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>46171</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>46170</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>46174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45936</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45373</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44844</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45502</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>46174</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>46174</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>46174</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>45373</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>45391</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>45453</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44809</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45439</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45105</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45455</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45469</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>44497</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>44957</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>46181</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>46181</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>46181</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>46176</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45162</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>46184</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45495</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>46184</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>46184</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>46182</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45958</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>46185</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>46185</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44631</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>46181</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45224</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45481</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>45964</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>46189</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>46189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45964</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>46189</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45089</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45964</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44501</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45104</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45664</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45664</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45434</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45715</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45664</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46198</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>46196</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>46196</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46184</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>46198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45708</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45533</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45484</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>45987</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45473</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>46210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46210</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>46210</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45253</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46210</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44950</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44950</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>46216</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>46216</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>44999</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46001</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>45777</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45303</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45559</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>46230</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45601</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46230</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46230</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>46230</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45470</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46237</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46237</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45667</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46010</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45407</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>46010</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>46281</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45569</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>46030</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>46030</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>46030</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>46283</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45617</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45720</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46042</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>46287</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>46042</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>46042</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46030</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45680</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>46043</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45303</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>46045</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>46289</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46290</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>46290</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>46290</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>46290</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>46290</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>46290</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>46289</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>46069</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>46069</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44517</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>46071</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45825</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>44498</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45642</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>44648</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45485</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45485</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>44662</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44855</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>44739</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45733</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>45485</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>46253</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>46252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46080</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>46252</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>46252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46297</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>46297</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>45835</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>46297</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>46297</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>46095</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>46297</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>46254</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>46297</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>46297</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>46297</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>46297</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>46297</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45235</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45427</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45586</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45742</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45572</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45257</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45481</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>46112</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46258</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46112</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>46112</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>46303</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46120</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>46127</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>44999</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>44999</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>44915</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>44642</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>45827</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>44552</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>46309</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>44995</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>46309</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45904</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>44959</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>45348</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45072</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45937</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46268</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44812</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45364</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46314</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>46230</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45975</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46230</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>44615</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45132</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45322</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>46314</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45103</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45834</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>46030</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44950</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45510</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>44568</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>45933</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44676</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>45030</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45408</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45587</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45714</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45707</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45385</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>46142</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>46275</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>44593</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45404</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46275</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>46142</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>46142</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>46142</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>44734</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45964</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44641</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>46154</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45896</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45790</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45303</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45115</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45027</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45226</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45267</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44609</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44828</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45506</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45022</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>44999</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45607</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45158</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>45656</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>44753</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44748</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45719</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45517</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>45511</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>44573</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45072</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45741</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44595</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45105</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>45510</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>44859</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45391</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45115</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45115</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44608</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44503</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>44907</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45254</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45609</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45525</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>44558</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45078</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45000</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45608</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44494</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45303</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45511</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45572</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>44866</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45190</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>44608</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44608</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44967</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45327</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>45162</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44578</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>45104</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>44602</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>44662</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45198</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>44697</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>44606</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>44641</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45217</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45072</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45191</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45162</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>45198</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45456</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44808</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45254</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45208</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44804</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45188</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45307</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45285</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44734</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45448</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>44687</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45471</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45007</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45301</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45441</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>44889</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45327</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45107</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>44865</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>45453</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45453</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45525</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>44573</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>44610</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>44909</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>43993</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>44655</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>46219</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>46286</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>46288</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>46268</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
